--- a/data/input_data.xlsx
+++ b/data/input_data.xlsx
@@ -10501,7 +10501,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="str">
-        <v>R02</v>
+        <v>R01</v>
       </c>
       <c r="D6" t="str">
         <v>Makassar</v>
@@ -10637,7 +10637,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="str">
-        <v>R03</v>
+        <v>R02</v>
       </c>
       <c r="D11" t="str">
         <v>TPK Makassar</v>
@@ -10779,7 +10779,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="str">
-        <v>R04</v>
+        <v>R03</v>
       </c>
       <c r="D16" t="str">
         <v>Samarinda</v>
@@ -11069,7 +11069,7 @@
         <v>9</v>
       </c>
       <c r="C26" t="str">
-        <v>R06</v>
+        <v>R05</v>
       </c>
       <c r="D26" t="str">
         <v>Bitung</v>
@@ -11205,7 +11205,7 @@
         <v>9</v>
       </c>
       <c r="C31" t="str">
-        <v>R07</v>
+        <v>R06</v>
       </c>
       <c r="D31" t="str">
         <v>TPK Bitung</v>
@@ -11347,7 +11347,7 @@
         <v>9</v>
       </c>
       <c r="C36" t="str">
-        <v>R08</v>
+        <v>R07</v>
       </c>
       <c r="D36" t="str">
         <v>Ambon</v>
@@ -11492,7 +11492,7 @@
         <v>9</v>
       </c>
       <c r="C41" t="str">
-        <v>R09</v>
+        <v>R08</v>
       </c>
       <c r="D41" t="str">
         <v>Sorong</v>
@@ -11637,7 +11637,7 @@
         <v>9</v>
       </c>
       <c r="C46" t="str">
-        <v>R10</v>
+        <v>R09</v>
       </c>
       <c r="D46" t="str">
         <v>Jayapura</v>
@@ -11782,7 +11782,7 @@
         <v>9</v>
       </c>
       <c r="C51" t="str">
-        <v>R11</v>
+        <v>R10</v>
       </c>
       <c r="D51" t="str">
         <v>Tarakan</v>
@@ -11927,7 +11927,7 @@
         <v>9</v>
       </c>
       <c r="C56" t="str">
-        <v>R12</v>
+        <v>R11</v>
       </c>
       <c r="D56" t="str">
         <v>Pantoloan</v>
@@ -12072,7 +12072,7 @@
         <v>9</v>
       </c>
       <c r="C61" t="str">
-        <v>R13</v>
+        <v>R12</v>
       </c>
       <c r="D61" t="str">
         <v>Ternate</v>
@@ -12217,7 +12217,7 @@
         <v>9</v>
       </c>
       <c r="C66" t="str">
-        <v>R14</v>
+        <v>R13</v>
       </c>
       <c r="D66" t="str">
         <v>Kendari</v>
@@ -12362,7 +12362,7 @@
         <v>9</v>
       </c>
       <c r="C71" t="str">
-        <v>R15</v>
+        <v>R14</v>
       </c>
       <c r="D71" t="str">
         <v>Parepare</v>
@@ -12507,7 +12507,7 @@
         <v>9</v>
       </c>
       <c r="C76" t="str">
-        <v>R16</v>
+        <v>R15</v>
       </c>
       <c r="D76" t="str">
         <v>Biak</v>
@@ -12652,7 +12652,7 @@
         <v>9</v>
       </c>
       <c r="C81" t="str">
-        <v>R17</v>
+        <v>R16</v>
       </c>
       <c r="D81" t="str">
         <v>Merauke</v>
@@ -12797,7 +12797,7 @@
         <v>9</v>
       </c>
       <c r="C86" t="str">
-        <v>R18</v>
+        <v>R17</v>
       </c>
       <c r="D86" t="str">
         <v>Manokwari</v>
@@ -12942,7 +12942,7 @@
         <v>9</v>
       </c>
       <c r="C91" t="str">
-        <v>R19</v>
+        <v>R18</v>
       </c>
       <c r="D91" t="str">
         <v>Nunukan</v>
@@ -13087,7 +13087,7 @@
         <v>9</v>
       </c>
       <c r="C96" t="str">
-        <v>R20</v>
+        <v>R19</v>
       </c>
       <c r="D96" t="str">
         <v>Tg Redeb</v>
@@ -13232,7 +13232,7 @@
         <v>9</v>
       </c>
       <c r="C101" t="str">
-        <v>R21</v>
+        <v>R20</v>
       </c>
       <c r="D101" t="str">
         <v>Gorontalo</v>
@@ -13377,7 +13377,7 @@
         <v>9</v>
       </c>
       <c r="C106" t="str">
-        <v>R22</v>
+        <v>R21</v>
       </c>
       <c r="D106" t="str">
         <v>Fakfak</v>
@@ -13522,7 +13522,7 @@
         <v>9</v>
       </c>
       <c r="C111" t="str">
-        <v>R23</v>
+        <v>R22</v>
       </c>
       <c r="D111" t="str">
         <v>Tolitoli</v>
@@ -13667,7 +13667,7 @@
         <v>9</v>
       </c>
       <c r="C116" t="str">
-        <v>R24</v>
+        <v>R23</v>
       </c>
       <c r="D116" t="str">
         <v>Manado</v>
@@ -13803,7 +13803,7 @@
         <v>9</v>
       </c>
       <c r="C121" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D121" t="str">
         <v>Makassar New Port</v>
@@ -13945,7 +13945,7 @@
         <v>9</v>
       </c>
       <c r="C126" t="str">
-        <v>R26</v>
+        <v>R25</v>
       </c>
       <c r="D126" t="str">
         <v xml:space="preserve">Bontang  </v>
@@ -14078,7 +14078,7 @@
         <v>9</v>
       </c>
       <c r="C131" t="str">
-        <v>R27</v>
+        <v>R26</v>
       </c>
       <c r="D131" t="str">
         <v>KKT</v>
@@ -38789,7 +38789,7 @@
         <v>9</v>
       </c>
       <c r="C463" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D463" t="str">
         <v>Makassar New Port</v>
@@ -38821,7 +38821,7 @@
         <v>9</v>
       </c>
       <c r="C464" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D464" t="str">
         <v>Makassar New Port</v>
@@ -38847,7 +38847,7 @@
         <v>9</v>
       </c>
       <c r="C465" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D465" t="str">
         <v>Makassar New Port</v>
@@ -38873,7 +38873,7 @@
         <v>9</v>
       </c>
       <c r="C466" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D466" t="str">
         <v>Makassar New Port</v>
@@ -38905,7 +38905,7 @@
         <v>9</v>
       </c>
       <c r="C467" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D467" t="str">
         <v>Makassar New Port</v>
@@ -38937,7 +38937,7 @@
         <v>9</v>
       </c>
       <c r="C468" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D468" t="str">
         <v>Makassar New Port</v>
@@ -38969,7 +38969,7 @@
         <v>9</v>
       </c>
       <c r="C469" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D469" t="str">
         <v>Makassar New Port</v>
@@ -38995,7 +38995,7 @@
         <v>9</v>
       </c>
       <c r="C470" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D470" t="str">
         <v>Makassar New Port</v>
@@ -39021,7 +39021,7 @@
         <v>9</v>
       </c>
       <c r="C471" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D471" t="str">
         <v>Makassar New Port</v>
@@ -39050,7 +39050,7 @@
         <v>9</v>
       </c>
       <c r="C472" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D472" t="str">
         <v>Makassar New Port</v>
@@ -39079,7 +39079,7 @@
         <v>9</v>
       </c>
       <c r="C473" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D473" t="str">
         <v>Makassar New Port</v>
@@ -39105,7 +39105,7 @@
         <v>9</v>
       </c>
       <c r="C474" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D474" t="str">
         <v>Makassar New Port</v>
@@ -39131,7 +39131,7 @@
         <v>9</v>
       </c>
       <c r="C475" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D475" t="str">
         <v>Makassar New Port</v>
@@ -39157,7 +39157,7 @@
         <v>9</v>
       </c>
       <c r="C476" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D476" t="str">
         <v>Makassar New Port</v>
@@ -39183,7 +39183,7 @@
         <v>9</v>
       </c>
       <c r="C477" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D477" t="str">
         <v>Makassar New Port</v>
@@ -39209,7 +39209,7 @@
         <v>9</v>
       </c>
       <c r="C478" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D478" t="str">
         <v>Makassar New Port</v>
@@ -39238,7 +39238,7 @@
         <v>9</v>
       </c>
       <c r="C479" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D479" t="str">
         <v>Makassar New Port</v>
@@ -39264,7 +39264,7 @@
         <v>9</v>
       </c>
       <c r="C480" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D480" t="str">
         <v>Makassar New Port</v>
@@ -39290,7 +39290,7 @@
         <v>9</v>
       </c>
       <c r="C481" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D481" t="str">
         <v>Makassar New Port</v>
@@ -39316,7 +39316,7 @@
         <v>9</v>
       </c>
       <c r="C482" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D482" t="str">
         <v>Makassar New Port</v>
@@ -39342,7 +39342,7 @@
         <v>9</v>
       </c>
       <c r="C483" t="str">
-        <v>R25</v>
+        <v>R24</v>
       </c>
       <c r="D483" t="str">
         <v>Makassar New Port</v>

--- a/data/input_data.xlsx
+++ b/data/input_data.xlsx
@@ -17657,7 +17657,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H236"/>
+  <dimension ref="A1:H487"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17734,7 +17734,7 @@
         <v>TGH</v>
       </c>
       <c r="H3">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
@@ -17760,7 +17760,7 @@
         <v>TSD</v>
       </c>
       <c r="H4">
-        <v>3636</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="5">
@@ -17786,7 +17786,7 @@
         <v>TGH</v>
       </c>
       <c r="H5">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6">
@@ -17812,7 +17812,7 @@
         <v>TSD</v>
       </c>
       <c r="H6">
-        <v>1593</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="7">
@@ -17837,8 +17837,8 @@
       <c r="G7" t="str">
         <v>TGH</v>
       </c>
-      <c r="H7" t="str">
-        <v>-</v>
+      <c r="H7">
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -17863,8 +17863,8 @@
       <c r="G8" t="str">
         <v>TSD</v>
       </c>
-      <c r="H8" t="str">
-        <v>-</v>
+      <c r="H8">
+        <v>850</v>
       </c>
     </row>
     <row r="9">
@@ -17889,8 +17889,8 @@
       <c r="G9" t="str">
         <v>BSH</v>
       </c>
-      <c r="H9" t="str">
-        <v>-</v>
+      <c r="H9">
+        <v>26.5</v>
       </c>
     </row>
     <row r="10">
@@ -17915,8 +17915,8 @@
       <c r="G10" t="str">
         <v>BCH</v>
       </c>
-      <c r="H10" t="str">
-        <v>-</v>
+      <c r="H10">
+        <v>20.2</v>
       </c>
     </row>
     <row r="11">
@@ -17942,7 +17942,7 @@
         <v>WTP</v>
       </c>
       <c r="H11">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="12">
@@ -17967,8 +17967,8 @@
       <c r="G12" t="str">
         <v>TGH</v>
       </c>
-      <c r="H12">
-        <v>161</v>
+      <c r="H12" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="13">
@@ -17993,8 +17993,8 @@
       <c r="G13" t="str">
         <v>TSD</v>
       </c>
-      <c r="H13">
-        <v>3636</v>
+      <c r="H13" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="14">
@@ -18019,8 +18019,8 @@
       <c r="G14" t="str">
         <v>TGH</v>
       </c>
-      <c r="H14">
-        <v>104</v>
+      <c r="H14" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="15">
@@ -18045,8 +18045,8 @@
       <c r="G15" t="str">
         <v>TSD</v>
       </c>
-      <c r="H15">
-        <v>1593</v>
+      <c r="H15" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="16">
@@ -18123,8 +18123,8 @@
       <c r="G18" t="str">
         <v>BSH</v>
       </c>
-      <c r="H18" t="str">
-        <v>-</v>
+      <c r="H18">
+        <v>36.8</v>
       </c>
     </row>
     <row r="19">
@@ -18149,8 +18149,8 @@
       <c r="G19" t="str">
         <v>BCH</v>
       </c>
-      <c r="H19" t="str">
-        <v>-</v>
+      <c r="H19">
+        <v>28.5</v>
       </c>
     </row>
     <row r="20">
@@ -18176,7 +18176,7 @@
         <v>WTP</v>
       </c>
       <c r="H20">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="21">
@@ -18202,7 +18202,7 @@
         <v>TGH</v>
       </c>
       <c r="H21">
-        <v>161</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22">
@@ -18228,7 +18228,7 @@
         <v>TSD</v>
       </c>
       <c r="H22">
-        <v>3636</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="23">
@@ -18254,7 +18254,7 @@
         <v>TGH</v>
       </c>
       <c r="H23">
-        <v>104</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
@@ -18280,7 +18280,7 @@
         <v>TSD</v>
       </c>
       <c r="H24">
-        <v>1593</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="25">
@@ -18305,8 +18305,8 @@
       <c r="G25" t="str">
         <v>TGH</v>
       </c>
-      <c r="H25" t="str">
-        <v>-</v>
+      <c r="H25">
+        <v>38</v>
       </c>
     </row>
     <row r="26">
@@ -18331,8 +18331,8 @@
       <c r="G26" t="str">
         <v>TSD</v>
       </c>
-      <c r="H26" t="str">
-        <v>-</v>
+      <c r="H26">
+        <v>720</v>
       </c>
     </row>
     <row r="27">
@@ -18357,8 +18357,8 @@
       <c r="G27" t="str">
         <v>BSH</v>
       </c>
-      <c r="H27" t="str">
-        <v>-</v>
+      <c r="H27">
+        <v>18.2</v>
       </c>
     </row>
     <row r="28">
@@ -18383,8 +18383,8 @@
       <c r="G28" t="str">
         <v>BCH</v>
       </c>
-      <c r="H28" t="str">
-        <v>-</v>
+      <c r="H28">
+        <v>14.5</v>
       </c>
     </row>
     <row r="29">
@@ -18410,7 +18410,7 @@
         <v>WTP</v>
       </c>
       <c r="H29">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="30">
@@ -18436,7 +18436,7 @@
         <v>TGH</v>
       </c>
       <c r="H30">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31">
@@ -18462,7 +18462,7 @@
         <v>TSD</v>
       </c>
       <c r="H31">
-        <v>3636</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="32">
@@ -18488,7 +18488,7 @@
         <v>TGH</v>
       </c>
       <c r="H32">
-        <v>104</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33">
@@ -18514,7 +18514,7 @@
         <v>TSD</v>
       </c>
       <c r="H33">
-        <v>1593</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="34">
@@ -18539,8 +18539,8 @@
       <c r="G34" t="str">
         <v>TGH</v>
       </c>
-      <c r="H34" t="str">
-        <v>-</v>
+      <c r="H34">
+        <v>55</v>
       </c>
     </row>
     <row r="35">
@@ -18565,8 +18565,8 @@
       <c r="G35" t="str">
         <v>TSD</v>
       </c>
-      <c r="H35" t="str">
-        <v>-</v>
+      <c r="H35">
+        <v>980</v>
       </c>
     </row>
     <row r="36">
@@ -18591,8 +18591,8 @@
       <c r="G36" t="str">
         <v>BSH</v>
       </c>
-      <c r="H36" t="str">
-        <v>-</v>
+      <c r="H36">
+        <v>28</v>
       </c>
     </row>
     <row r="37">
@@ -18617,8 +18617,8 @@
       <c r="G37" t="str">
         <v>BCH</v>
       </c>
-      <c r="H37" t="str">
-        <v>-</v>
+      <c r="H37">
+        <v>21.5</v>
       </c>
     </row>
     <row r="38">
@@ -18644,7 +18644,7 @@
         <v>WTP</v>
       </c>
       <c r="H38">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39">
@@ -18670,7 +18670,7 @@
         <v>TGH</v>
       </c>
       <c r="H39">
-        <v>161</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40">
@@ -18696,7 +18696,7 @@
         <v>TSD</v>
       </c>
       <c r="H40">
-        <v>3636</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="41">
@@ -18722,7 +18722,7 @@
         <v>TGH</v>
       </c>
       <c r="H41">
-        <v>104</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42">
@@ -18748,7 +18748,7 @@
         <v>TSD</v>
       </c>
       <c r="H42">
-        <v>1593</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="43">
@@ -18773,8 +18773,8 @@
       <c r="G43" t="str">
         <v>TGH</v>
       </c>
-      <c r="H43" t="str">
-        <v>-</v>
+      <c r="H43">
+        <v>42</v>
       </c>
     </row>
     <row r="44">
@@ -18799,8 +18799,8 @@
       <c r="G44" t="str">
         <v>TSD</v>
       </c>
-      <c r="H44" t="str">
-        <v>-</v>
+      <c r="H44">
+        <v>780</v>
       </c>
     </row>
     <row r="45">
@@ -18825,8 +18825,8 @@
       <c r="G45" t="str">
         <v>BSH</v>
       </c>
-      <c r="H45" t="str">
-        <v>-</v>
+      <c r="H45">
+        <v>23.5</v>
       </c>
     </row>
     <row r="46">
@@ -18851,8 +18851,8 @@
       <c r="G46" t="str">
         <v>BCH</v>
       </c>
-      <c r="H46" t="str">
-        <v>-</v>
+      <c r="H46">
+        <v>17.8</v>
       </c>
     </row>
     <row r="47">
@@ -18878,7 +18878,7 @@
         <v>WTP</v>
       </c>
       <c r="H47">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="48">
@@ -18903,8 +18903,8 @@
       <c r="G48" t="str">
         <v>TGH</v>
       </c>
-      <c r="H48">
-        <v>161</v>
+      <c r="H48" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="49">
@@ -18929,8 +18929,8 @@
       <c r="G49" t="str">
         <v>TSD</v>
       </c>
-      <c r="H49">
-        <v>3636</v>
+      <c r="H49" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="50">
@@ -18955,8 +18955,8 @@
       <c r="G50" t="str">
         <v>TGH</v>
       </c>
-      <c r="H50">
-        <v>104</v>
+      <c r="H50" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="51">
@@ -18981,8 +18981,8 @@
       <c r="G51" t="str">
         <v>TSD</v>
       </c>
-      <c r="H51">
-        <v>1593</v>
+      <c r="H51" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="52">
@@ -19059,8 +19059,8 @@
       <c r="G54" t="str">
         <v>BSH</v>
       </c>
-      <c r="H54" t="str">
-        <v>-</v>
+      <c r="H54">
+        <v>32.5</v>
       </c>
     </row>
     <row r="55">
@@ -19085,8 +19085,8 @@
       <c r="G55" t="str">
         <v>BCH</v>
       </c>
-      <c r="H55" t="str">
-        <v>-</v>
+      <c r="H55">
+        <v>25.2</v>
       </c>
     </row>
     <row r="56">
@@ -19112,7 +19112,7 @@
         <v>WTP</v>
       </c>
       <c r="H56">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="57">
@@ -19138,7 +19138,7 @@
         <v>TGH</v>
       </c>
       <c r="H57">
-        <v>161</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58">
@@ -19164,7 +19164,7 @@
         <v>TSD</v>
       </c>
       <c r="H58">
-        <v>3636</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="59">
@@ -19190,7 +19190,7 @@
         <v>TGH</v>
       </c>
       <c r="H59">
-        <v>104</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
@@ -19216,7 +19216,7 @@
         <v>TSD</v>
       </c>
       <c r="H60">
-        <v>1593</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="61">
@@ -19241,8 +19241,8 @@
       <c r="G61" t="str">
         <v>TGH</v>
       </c>
-      <c r="H61" t="str">
-        <v>-</v>
+      <c r="H61">
+        <v>34</v>
       </c>
     </row>
     <row r="62">
@@ -19267,8 +19267,8 @@
       <c r="G62" t="str">
         <v>TSD</v>
       </c>
-      <c r="H62" t="str">
-        <v>-</v>
+      <c r="H62">
+        <v>620</v>
       </c>
     </row>
     <row r="63">
@@ -19293,8 +19293,8 @@
       <c r="G63" t="str">
         <v>BSH</v>
       </c>
-      <c r="H63" t="str">
-        <v>-</v>
+      <c r="H63">
+        <v>21.4</v>
       </c>
     </row>
     <row r="64">
@@ -19319,8 +19319,8 @@
       <c r="G64" t="str">
         <v>BCH</v>
       </c>
-      <c r="H64" t="str">
-        <v>-</v>
+      <c r="H64">
+        <v>16.2</v>
       </c>
     </row>
     <row r="65">
@@ -19346,7 +19346,7 @@
         <v>WTP</v>
       </c>
       <c r="H65">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="66">
@@ -19372,7 +19372,7 @@
         <v>TGH</v>
       </c>
       <c r="H66">
-        <v>161</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67">
@@ -19398,7 +19398,7 @@
         <v>TSD</v>
       </c>
       <c r="H67">
-        <v>3636</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="68">
@@ -19424,7 +19424,7 @@
         <v>TGH</v>
       </c>
       <c r="H68">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69">
@@ -19450,7 +19450,7 @@
         <v>TSD</v>
       </c>
       <c r="H69">
-        <v>1593</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="70">
@@ -19475,8 +19475,8 @@
       <c r="G70" t="str">
         <v>TGH</v>
       </c>
-      <c r="H70" t="str">
-        <v>-</v>
+      <c r="H70">
+        <v>32</v>
       </c>
     </row>
     <row r="71">
@@ -19501,8 +19501,8 @@
       <c r="G71" t="str">
         <v>TSD</v>
       </c>
-      <c r="H71" t="str">
-        <v>-</v>
+      <c r="H71">
+        <v>560</v>
       </c>
     </row>
     <row r="72">
@@ -19527,8 +19527,8 @@
       <c r="G72" t="str">
         <v>BSH</v>
       </c>
-      <c r="H72" t="str">
-        <v>-</v>
+      <c r="H72">
+        <v>20.2</v>
       </c>
     </row>
     <row r="73">
@@ -19553,8 +19553,8 @@
       <c r="G73" t="str">
         <v>BCH</v>
       </c>
-      <c r="H73" t="str">
-        <v>-</v>
+      <c r="H73">
+        <v>15.4</v>
       </c>
     </row>
     <row r="74">
@@ -19580,7 +19580,7 @@
         <v>WTP</v>
       </c>
       <c r="H74">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="75">
@@ -19606,7 +19606,7 @@
         <v>TGH</v>
       </c>
       <c r="H75">
-        <v>161</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76">
@@ -19632,7 +19632,7 @@
         <v>TSD</v>
       </c>
       <c r="H76">
-        <v>3636</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="77">
@@ -19658,7 +19658,7 @@
         <v>TGH</v>
       </c>
       <c r="H77">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78">
@@ -19684,7 +19684,7 @@
         <v>TSD</v>
       </c>
       <c r="H78">
-        <v>1593</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="79">
@@ -19709,8 +19709,8 @@
       <c r="G79" t="str">
         <v>TGH</v>
       </c>
-      <c r="H79" t="str">
-        <v>-</v>
+      <c r="H79">
+        <v>31</v>
       </c>
     </row>
     <row r="80">
@@ -19735,8 +19735,8 @@
       <c r="G80" t="str">
         <v>TSD</v>
       </c>
-      <c r="H80" t="str">
-        <v>-</v>
+      <c r="H80">
+        <v>540</v>
       </c>
     </row>
     <row r="81">
@@ -19761,8 +19761,8 @@
       <c r="G81" t="str">
         <v>BSH</v>
       </c>
-      <c r="H81" t="str">
-        <v>-</v>
+      <c r="H81">
+        <v>20.5</v>
       </c>
     </row>
     <row r="82">
@@ -19787,8 +19787,8 @@
       <c r="G82" t="str">
         <v>BCH</v>
       </c>
-      <c r="H82" t="str">
-        <v>-</v>
+      <c r="H82">
+        <v>15.8</v>
       </c>
     </row>
     <row r="83">
@@ -19814,7 +19814,7 @@
         <v>WTP</v>
       </c>
       <c r="H83">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="84">
@@ -19840,7 +19840,7 @@
         <v>TGH</v>
       </c>
       <c r="H84">
-        <v>161</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85">
@@ -19866,7 +19866,7 @@
         <v>TSD</v>
       </c>
       <c r="H85">
-        <v>3636</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="86">
@@ -19892,7 +19892,7 @@
         <v>TGH</v>
       </c>
       <c r="H86">
-        <v>104</v>
+        <v>128</v>
       </c>
     </row>
     <row r="87">
@@ -19918,7 +19918,7 @@
         <v>TSD</v>
       </c>
       <c r="H87">
-        <v>1593</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="88">
@@ -19943,8 +19943,8 @@
       <c r="G88" t="str">
         <v>TGH</v>
       </c>
-      <c r="H88" t="str">
-        <v>-</v>
+      <c r="H88">
+        <v>38</v>
       </c>
     </row>
     <row r="89">
@@ -19969,8 +19969,8 @@
       <c r="G89" t="str">
         <v>TSD</v>
       </c>
-      <c r="H89" t="str">
-        <v>-</v>
+      <c r="H89">
+        <v>700</v>
       </c>
     </row>
     <row r="90">
@@ -19995,8 +19995,8 @@
       <c r="G90" t="str">
         <v>BSH</v>
       </c>
-      <c r="H90" t="str">
-        <v>-</v>
+      <c r="H90">
+        <v>19.8</v>
       </c>
     </row>
     <row r="91">
@@ -20021,8 +20021,8 @@
       <c r="G91" t="str">
         <v>BCH</v>
       </c>
-      <c r="H91" t="str">
-        <v>-</v>
+      <c r="H91">
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -20048,7 +20048,7 @@
         <v>WTP</v>
       </c>
       <c r="H92">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="93">
@@ -20074,7 +20074,7 @@
         <v>TGH</v>
       </c>
       <c r="H93">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="94">
@@ -20100,7 +20100,7 @@
         <v>TSD</v>
       </c>
       <c r="H94">
-        <v>3636</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="95">
@@ -20126,7 +20126,7 @@
         <v>TGH</v>
       </c>
       <c r="H95">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96">
@@ -20152,7 +20152,7 @@
         <v>TSD</v>
       </c>
       <c r="H96">
-        <v>1593</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="97">
@@ -20177,8 +20177,8 @@
       <c r="G97" t="str">
         <v>TGH</v>
       </c>
-      <c r="H97" t="str">
-        <v>-</v>
+      <c r="H97">
+        <v>40</v>
       </c>
     </row>
     <row r="98">
@@ -20203,8 +20203,8 @@
       <c r="G98" t="str">
         <v>TSD</v>
       </c>
-      <c r="H98" t="str">
-        <v>-</v>
+      <c r="H98">
+        <v>740</v>
       </c>
     </row>
     <row r="99">
@@ -20229,8 +20229,8 @@
       <c r="G99" t="str">
         <v>BSH</v>
       </c>
-      <c r="H99" t="str">
-        <v>-</v>
+      <c r="H99">
+        <v>23.2</v>
       </c>
     </row>
     <row r="100">
@@ -20255,8 +20255,8 @@
       <c r="G100" t="str">
         <v>BCH</v>
       </c>
-      <c r="H100" t="str">
-        <v>-</v>
+      <c r="H100">
+        <v>17.8</v>
       </c>
     </row>
     <row r="101">
@@ -20282,7 +20282,7 @@
         <v>WTP</v>
       </c>
       <c r="H101">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="102">
@@ -20308,7 +20308,7 @@
         <v>TGH</v>
       </c>
       <c r="H102">
-        <v>161</v>
+        <v>125</v>
       </c>
     </row>
     <row r="103">
@@ -20334,7 +20334,7 @@
         <v>TSD</v>
       </c>
       <c r="H103">
-        <v>3636</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="104">
@@ -20360,7 +20360,7 @@
         <v>TGH</v>
       </c>
       <c r="H104">
-        <v>104</v>
+        <v>85</v>
       </c>
     </row>
     <row r="105">
@@ -20386,7 +20386,7 @@
         <v>TSD</v>
       </c>
       <c r="H105">
-        <v>1593</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="106">
@@ -20411,8 +20411,8 @@
       <c r="G106" t="str">
         <v>TGH</v>
       </c>
-      <c r="H106" t="str">
-        <v>-</v>
+      <c r="H106">
+        <v>35</v>
       </c>
     </row>
     <row r="107">
@@ -20437,8 +20437,8 @@
       <c r="G107" t="str">
         <v>TSD</v>
       </c>
-      <c r="H107" t="str">
-        <v>-</v>
+      <c r="H107">
+        <v>630</v>
       </c>
     </row>
     <row r="108">
@@ -20463,8 +20463,8 @@
       <c r="G108" t="str">
         <v>BSH</v>
       </c>
-      <c r="H108" t="str">
-        <v>-</v>
+      <c r="H108">
+        <v>19.5</v>
       </c>
     </row>
     <row r="109">
@@ -20489,8 +20489,8 @@
       <c r="G109" t="str">
         <v>BCH</v>
       </c>
-      <c r="H109" t="str">
-        <v>-</v>
+      <c r="H109">
+        <v>15.1</v>
       </c>
     </row>
     <row r="110">
@@ -20516,7 +20516,7 @@
         <v>WTP</v>
       </c>
       <c r="H110">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="111">
@@ -20542,7 +20542,7 @@
         <v>TGH</v>
       </c>
       <c r="H111">
-        <v>161</v>
+        <v>215</v>
       </c>
     </row>
     <row r="112">
@@ -20568,7 +20568,7 @@
         <v>TSD</v>
       </c>
       <c r="H112">
-        <v>3636</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="113">
@@ -20594,7 +20594,7 @@
         <v>TGH</v>
       </c>
       <c r="H113">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="114">
@@ -20620,7 +20620,7 @@
         <v>TSD</v>
       </c>
       <c r="H114">
-        <v>1593</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="115">
@@ -20645,8 +20645,8 @@
       <c r="G115" t="str">
         <v>TGH</v>
       </c>
-      <c r="H115" t="str">
-        <v>-</v>
+      <c r="H115">
+        <v>44</v>
       </c>
     </row>
     <row r="116">
@@ -20671,8 +20671,8 @@
       <c r="G116" t="str">
         <v>TSD</v>
       </c>
-      <c r="H116" t="str">
-        <v>-</v>
+      <c r="H116">
+        <v>810</v>
       </c>
     </row>
     <row r="117">
@@ -20697,8 +20697,8 @@
       <c r="G117" t="str">
         <v>BSH</v>
       </c>
-      <c r="H117" t="str">
-        <v>-</v>
+      <c r="H117">
+        <v>24.5</v>
       </c>
     </row>
     <row r="118">
@@ -20723,8 +20723,8 @@
       <c r="G118" t="str">
         <v>BCH</v>
       </c>
-      <c r="H118" t="str">
-        <v>-</v>
+      <c r="H118">
+        <v>18.9</v>
       </c>
     </row>
     <row r="119">
@@ -20750,7 +20750,7 @@
         <v>WTP</v>
       </c>
       <c r="H119">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="120">
@@ -20776,7 +20776,7 @@
         <v>TGH</v>
       </c>
       <c r="H120">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="121">
@@ -20802,7 +20802,7 @@
         <v>TSD</v>
       </c>
       <c r="H121">
-        <v>3636</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="122">
@@ -20828,7 +20828,7 @@
         <v>TGH</v>
       </c>
       <c r="H122">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="123">
@@ -20854,7 +20854,7 @@
         <v>TSD</v>
       </c>
       <c r="H123">
-        <v>1593</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="124">
@@ -20879,8 +20879,8 @@
       <c r="G124" t="str">
         <v>TGH</v>
       </c>
-      <c r="H124" t="str">
-        <v>-</v>
+      <c r="H124">
+        <v>40</v>
       </c>
     </row>
     <row r="125">
@@ -20905,8 +20905,8 @@
       <c r="G125" t="str">
         <v>TSD</v>
       </c>
-      <c r="H125" t="str">
-        <v>-</v>
+      <c r="H125">
+        <v>730</v>
       </c>
     </row>
     <row r="126">
@@ -20931,8 +20931,8 @@
       <c r="G126" t="str">
         <v>BSH</v>
       </c>
-      <c r="H126" t="str">
-        <v>-</v>
+      <c r="H126">
+        <v>16.8</v>
       </c>
     </row>
     <row r="127">
@@ -20957,8 +20957,8 @@
       <c r="G127" t="str">
         <v>BCH</v>
       </c>
-      <c r="H127" t="str">
-        <v>-</v>
+      <c r="H127">
+        <v>13</v>
       </c>
     </row>
     <row r="128">
@@ -20984,7 +20984,7 @@
         <v>WTP</v>
       </c>
       <c r="H128">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="129">
@@ -21010,7 +21010,7 @@
         <v>TGH</v>
       </c>
       <c r="H129">
-        <v>161</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130">
@@ -21036,7 +21036,7 @@
         <v>TSD</v>
       </c>
       <c r="H130">
-        <v>3636</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="131">
@@ -21062,7 +21062,7 @@
         <v>TGH</v>
       </c>
       <c r="H131">
-        <v>104</v>
+        <v>70</v>
       </c>
     </row>
     <row r="132">
@@ -21088,7 +21088,7 @@
         <v>TSD</v>
       </c>
       <c r="H132">
-        <v>1593</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="133">
@@ -21113,8 +21113,8 @@
       <c r="G133" t="str">
         <v>TGH</v>
       </c>
-      <c r="H133" t="str">
-        <v>-</v>
+      <c r="H133">
+        <v>28</v>
       </c>
     </row>
     <row r="134">
@@ -21139,8 +21139,8 @@
       <c r="G134" t="str">
         <v>TSD</v>
       </c>
-      <c r="H134" t="str">
-        <v>-</v>
+      <c r="H134">
+        <v>490</v>
       </c>
     </row>
     <row r="135">
@@ -21165,8 +21165,8 @@
       <c r="G135" t="str">
         <v>BSH</v>
       </c>
-      <c r="H135" t="str">
-        <v>-</v>
+      <c r="H135">
+        <v>17.2</v>
       </c>
     </row>
     <row r="136">
@@ -21191,8 +21191,8 @@
       <c r="G136" t="str">
         <v>BCH</v>
       </c>
-      <c r="H136" t="str">
-        <v>-</v>
+      <c r="H136">
+        <v>13.5</v>
       </c>
     </row>
     <row r="137">
@@ -21218,7 +21218,7 @@
         <v>WTP</v>
       </c>
       <c r="H137">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="138">
@@ -21244,7 +21244,7 @@
         <v>TGH</v>
       </c>
       <c r="H138">
-        <v>161</v>
+        <v>72</v>
       </c>
     </row>
     <row r="139">
@@ -21270,7 +21270,7 @@
         <v>TSD</v>
       </c>
       <c r="H139">
-        <v>3636</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="140">
@@ -21296,7 +21296,7 @@
         <v>TGH</v>
       </c>
       <c r="H140">
-        <v>104</v>
+        <v>66</v>
       </c>
     </row>
     <row r="141">
@@ -21322,7 +21322,7 @@
         <v>TSD</v>
       </c>
       <c r="H141">
-        <v>1593</v>
+        <v>980</v>
       </c>
     </row>
     <row r="142">
@@ -21347,8 +21347,8 @@
       <c r="G142" t="str">
         <v>TGH</v>
       </c>
-      <c r="H142" t="str">
-        <v>-</v>
+      <c r="H142">
+        <v>27</v>
       </c>
     </row>
     <row r="143">
@@ -21373,8 +21373,8 @@
       <c r="G143" t="str">
         <v>TSD</v>
       </c>
-      <c r="H143" t="str">
-        <v>-</v>
+      <c r="H143">
+        <v>470</v>
       </c>
     </row>
     <row r="144">
@@ -21399,8 +21399,8 @@
       <c r="G144" t="str">
         <v>BSH</v>
       </c>
-      <c r="H144" t="str">
-        <v>-</v>
+      <c r="H144">
+        <v>16.2</v>
       </c>
     </row>
     <row r="145">
@@ -21425,8 +21425,8 @@
       <c r="G145" t="str">
         <v>BCH</v>
       </c>
-      <c r="H145" t="str">
-        <v>-</v>
+      <c r="H145">
+        <v>12.6</v>
       </c>
     </row>
     <row r="146">
@@ -21452,7 +21452,7 @@
         <v>WTP</v>
       </c>
       <c r="H146">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="147">
@@ -21478,7 +21478,7 @@
         <v>TGH</v>
       </c>
       <c r="H147">
-        <v>161</v>
+        <v>80</v>
       </c>
     </row>
     <row r="148">
@@ -21504,7 +21504,7 @@
         <v>TSD</v>
       </c>
       <c r="H148">
-        <v>3636</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="149">
@@ -21530,7 +21530,7 @@
         <v>TGH</v>
       </c>
       <c r="H149">
-        <v>104</v>
+        <v>75</v>
       </c>
     </row>
     <row r="150">
@@ -21556,7 +21556,7 @@
         <v>TSD</v>
       </c>
       <c r="H150">
-        <v>1593</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="151">
@@ -21581,8 +21581,8 @@
       <c r="G151" t="str">
         <v>TGH</v>
       </c>
-      <c r="H151" t="str">
-        <v>-</v>
+      <c r="H151">
+        <v>30</v>
       </c>
     </row>
     <row r="152">
@@ -21607,8 +21607,8 @@
       <c r="G152" t="str">
         <v>TSD</v>
       </c>
-      <c r="H152" t="str">
-        <v>-</v>
+      <c r="H152">
+        <v>530</v>
       </c>
     </row>
     <row r="153">
@@ -21633,8 +21633,8 @@
       <c r="G153" t="str">
         <v>BSH</v>
       </c>
-      <c r="H153" t="str">
-        <v>-</v>
+      <c r="H153">
+        <v>18.5</v>
       </c>
     </row>
     <row r="154">
@@ -21659,8 +21659,8 @@
       <c r="G154" t="str">
         <v>BCH</v>
       </c>
-      <c r="H154" t="str">
-        <v>-</v>
+      <c r="H154">
+        <v>14.2</v>
       </c>
     </row>
     <row r="155">
@@ -21686,7 +21686,7 @@
         <v>WTP</v>
       </c>
       <c r="H155">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="156">
@@ -21712,7 +21712,7 @@
         <v>TGH</v>
       </c>
       <c r="H156">
-        <v>161</v>
+        <v>78</v>
       </c>
     </row>
     <row r="157">
@@ -21738,7 +21738,7 @@
         <v>TSD</v>
       </c>
       <c r="H157">
-        <v>3636</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="158">
@@ -21764,7 +21764,7 @@
         <v>TGH</v>
       </c>
       <c r="H158">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="159">
@@ -21790,7 +21790,7 @@
         <v>TSD</v>
       </c>
       <c r="H159">
-        <v>1593</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="160">
@@ -21815,8 +21815,8 @@
       <c r="G160" t="str">
         <v>TGH</v>
       </c>
-      <c r="H160" t="str">
-        <v>-</v>
+      <c r="H160">
+        <v>30</v>
       </c>
     </row>
     <row r="161">
@@ -21841,8 +21841,8 @@
       <c r="G161" t="str">
         <v>TSD</v>
       </c>
-      <c r="H161" t="str">
-        <v>-</v>
+      <c r="H161">
+        <v>510</v>
       </c>
     </row>
     <row r="162">
@@ -21867,8 +21867,8 @@
       <c r="G162" t="str">
         <v>BSH</v>
       </c>
-      <c r="H162" t="str">
-        <v>-</v>
+      <c r="H162">
+        <v>16.8</v>
       </c>
     </row>
     <row r="163">
@@ -21893,8 +21893,8 @@
       <c r="G163" t="str">
         <v>BCH</v>
       </c>
-      <c r="H163" t="str">
-        <v>-</v>
+      <c r="H163">
+        <v>13.1</v>
       </c>
     </row>
     <row r="164">
@@ -21920,7 +21920,7 @@
         <v>WTP</v>
       </c>
       <c r="H164">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="165">
@@ -21946,7 +21946,7 @@
         <v>TGH</v>
       </c>
       <c r="H165">
-        <v>161</v>
+        <v>295</v>
       </c>
     </row>
     <row r="166">
@@ -21972,7 +21972,7 @@
         <v>TSD</v>
       </c>
       <c r="H166">
-        <v>3636</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="167">
@@ -21998,7 +21998,7 @@
         <v>TGH</v>
       </c>
       <c r="H167">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="168">
@@ -22024,7 +22024,7 @@
         <v>TSD</v>
       </c>
       <c r="H168">
-        <v>1593</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="169">
@@ -22049,8 +22049,8 @@
       <c r="G169" t="str">
         <v>TGH</v>
       </c>
-      <c r="H169" t="str">
-        <v>-</v>
+      <c r="H169">
+        <v>34</v>
       </c>
     </row>
     <row r="170">
@@ -22075,8 +22075,8 @@
       <c r="G170" t="str">
         <v>TSD</v>
       </c>
-      <c r="H170" t="str">
-        <v>-</v>
+      <c r="H170">
+        <v>610</v>
       </c>
     </row>
     <row r="171">
@@ -22101,8 +22101,8 @@
       <c r="G171" t="str">
         <v>BSH</v>
       </c>
-      <c r="H171" t="str">
-        <v>-</v>
+      <c r="H171">
+        <v>16</v>
       </c>
     </row>
     <row r="172">
@@ -22127,8 +22127,8 @@
       <c r="G172" t="str">
         <v>BCH</v>
       </c>
-      <c r="H172" t="str">
-        <v>-</v>
+      <c r="H172">
+        <v>12.4</v>
       </c>
     </row>
     <row r="173">
@@ -22154,7 +22154,7 @@
         <v>WTP</v>
       </c>
       <c r="H173">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="174">
@@ -22180,7 +22180,7 @@
         <v>TGH</v>
       </c>
       <c r="H174">
-        <v>161</v>
+        <v>125</v>
       </c>
     </row>
     <row r="175">
@@ -22206,7 +22206,7 @@
         <v>TSD</v>
       </c>
       <c r="H175">
-        <v>3636</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="176">
@@ -22232,7 +22232,7 @@
         <v>TGH</v>
       </c>
       <c r="H176">
-        <v>104</v>
+        <v>82</v>
       </c>
     </row>
     <row r="177">
@@ -22258,7 +22258,7 @@
         <v>TSD</v>
       </c>
       <c r="H177">
-        <v>1593</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="178">
@@ -22283,8 +22283,8 @@
       <c r="G178" t="str">
         <v>TGH</v>
       </c>
-      <c r="H178" t="str">
-        <v>-</v>
+      <c r="H178">
+        <v>33</v>
       </c>
     </row>
     <row r="179">
@@ -22309,8 +22309,8 @@
       <c r="G179" t="str">
         <v>TSD</v>
       </c>
-      <c r="H179" t="str">
-        <v>-</v>
+      <c r="H179">
+        <v>590</v>
       </c>
     </row>
     <row r="180">
@@ -22335,8 +22335,8 @@
       <c r="G180" t="str">
         <v>BSH</v>
       </c>
-      <c r="H180" t="str">
-        <v>-</v>
+      <c r="H180">
+        <v>18</v>
       </c>
     </row>
     <row r="181">
@@ -22361,8 +22361,8 @@
       <c r="G181" t="str">
         <v>BCH</v>
       </c>
-      <c r="H181" t="str">
-        <v>-</v>
+      <c r="H181">
+        <v>13.8</v>
       </c>
     </row>
     <row r="182">
@@ -22388,7 +22388,7 @@
         <v>WTP</v>
       </c>
       <c r="H182">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="183">
@@ -22414,7 +22414,7 @@
         <v>TGH</v>
       </c>
       <c r="H183">
-        <v>161</v>
+        <v>65</v>
       </c>
     </row>
     <row r="184">
@@ -22440,7 +22440,7 @@
         <v>TSD</v>
       </c>
       <c r="H184">
-        <v>3636</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="185">
@@ -22466,7 +22466,7 @@
         <v>TGH</v>
       </c>
       <c r="H185">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="186">
@@ -22492,7 +22492,7 @@
         <v>TSD</v>
       </c>
       <c r="H186">
-        <v>1593</v>
+        <v>880</v>
       </c>
     </row>
     <row r="187">
@@ -22517,8 +22517,8 @@
       <c r="G187" t="str">
         <v>TGH</v>
       </c>
-      <c r="H187" t="str">
-        <v>-</v>
+      <c r="H187">
+        <v>25</v>
       </c>
     </row>
     <row r="188">
@@ -22543,8 +22543,8 @@
       <c r="G188" t="str">
         <v>TSD</v>
       </c>
-      <c r="H188" t="str">
-        <v>-</v>
+      <c r="H188">
+        <v>430</v>
       </c>
     </row>
     <row r="189">
@@ -22569,8 +22569,8 @@
       <c r="G189" t="str">
         <v>BSH</v>
       </c>
-      <c r="H189" t="str">
-        <v>-</v>
+      <c r="H189">
+        <v>15</v>
       </c>
     </row>
     <row r="190">
@@ -22595,8 +22595,8 @@
       <c r="G190" t="str">
         <v>BCH</v>
       </c>
-      <c r="H190" t="str">
-        <v>-</v>
+      <c r="H190">
+        <v>11.6</v>
       </c>
     </row>
     <row r="191">
@@ -22622,7 +22622,7 @@
         <v>WTP</v>
       </c>
       <c r="H191">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="192">
@@ -22648,7 +22648,7 @@
         <v>TGH</v>
       </c>
       <c r="H192">
-        <v>161</v>
+        <v>70</v>
       </c>
     </row>
     <row r="193">
@@ -22674,7 +22674,7 @@
         <v>TSD</v>
       </c>
       <c r="H193">
-        <v>3636</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="194">
@@ -22700,7 +22700,7 @@
         <v>TGH</v>
       </c>
       <c r="H194">
-        <v>104</v>
+        <v>64</v>
       </c>
     </row>
     <row r="195">
@@ -22726,7 +22726,7 @@
         <v>TSD</v>
       </c>
       <c r="H195">
-        <v>1593</v>
+        <v>950</v>
       </c>
     </row>
     <row r="196">
@@ -22751,8 +22751,8 @@
       <c r="G196" t="str">
         <v>TGH</v>
       </c>
-      <c r="H196" t="str">
-        <v>-</v>
+      <c r="H196">
+        <v>26</v>
       </c>
     </row>
     <row r="197">
@@ -22777,8 +22777,8 @@
       <c r="G197" t="str">
         <v>TSD</v>
       </c>
-      <c r="H197" t="str">
-        <v>-</v>
+      <c r="H197">
+        <v>450</v>
       </c>
     </row>
     <row r="198">
@@ -22803,8 +22803,8 @@
       <c r="G198" t="str">
         <v>BSH</v>
       </c>
-      <c r="H198" t="str">
-        <v>-</v>
+      <c r="H198">
+        <v>15.2</v>
       </c>
     </row>
     <row r="199">
@@ -22829,8 +22829,8 @@
       <c r="G199" t="str">
         <v>BCH</v>
       </c>
-      <c r="H199" t="str">
-        <v>-</v>
+      <c r="H199">
+        <v>11.9</v>
       </c>
     </row>
     <row r="200">
@@ -22882,7 +22882,7 @@
         <v>TGH</v>
       </c>
       <c r="H201">
-        <v>161</v>
+        <v>55</v>
       </c>
     </row>
     <row r="202">
@@ -22908,7 +22908,7 @@
         <v>TSD</v>
       </c>
       <c r="H202">
-        <v>3636</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="203">
@@ -22934,7 +22934,7 @@
         <v>TGH</v>
       </c>
       <c r="H203">
-        <v>104</v>
+        <v>50</v>
       </c>
     </row>
     <row r="204">
@@ -22960,7 +22960,7 @@
         <v>TSD</v>
       </c>
       <c r="H204">
-        <v>1593</v>
+        <v>750</v>
       </c>
     </row>
     <row r="205">
@@ -22985,8 +22985,8 @@
       <c r="G205" t="str">
         <v>TGH</v>
       </c>
-      <c r="H205" t="str">
-        <v>-</v>
+      <c r="H205">
+        <v>24</v>
       </c>
     </row>
     <row r="206">
@@ -23011,8 +23011,8 @@
       <c r="G206" t="str">
         <v>TSD</v>
       </c>
-      <c r="H206" t="str">
-        <v>-</v>
+      <c r="H206">
+        <v>410</v>
       </c>
     </row>
     <row r="207">
@@ -23037,8 +23037,8 @@
       <c r="G207" t="str">
         <v>BSH</v>
       </c>
-      <c r="H207" t="str">
-        <v>-</v>
+      <c r="H207">
+        <v>14.5</v>
       </c>
     </row>
     <row r="208">
@@ -23063,8 +23063,8 @@
       <c r="G208" t="str">
         <v>BCH</v>
       </c>
-      <c r="H208" t="str">
-        <v>-</v>
+      <c r="H208">
+        <v>11.2</v>
       </c>
     </row>
     <row r="209">
@@ -23090,7 +23090,7 @@
         <v>WTP</v>
       </c>
       <c r="H209">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="210">
@@ -23115,8 +23115,8 @@
       <c r="G210" t="str">
         <v>TGH</v>
       </c>
-      <c r="H210">
-        <v>161</v>
+      <c r="H210" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="211">
@@ -23141,8 +23141,8 @@
       <c r="G211" t="str">
         <v>TSD</v>
       </c>
-      <c r="H211">
-        <v>3636</v>
+      <c r="H211" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="212">
@@ -23167,8 +23167,8 @@
       <c r="G212" t="str">
         <v>TGH</v>
       </c>
-      <c r="H212">
-        <v>104</v>
+      <c r="H212" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="213">
@@ -23193,8 +23193,8 @@
       <c r="G213" t="str">
         <v>TSD</v>
       </c>
-      <c r="H213">
-        <v>1593</v>
+      <c r="H213" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="214">
@@ -23271,8 +23271,8 @@
       <c r="G216" t="str">
         <v>BSH</v>
       </c>
-      <c r="H216" t="str">
-        <v>-</v>
+      <c r="H216">
+        <v>44.5</v>
       </c>
     </row>
     <row r="217">
@@ -23297,8 +23297,8 @@
       <c r="G217" t="str">
         <v>BCH</v>
       </c>
-      <c r="H217" t="str">
-        <v>-</v>
+      <c r="H217">
+        <v>34.2</v>
       </c>
     </row>
     <row r="218">
@@ -23312,7 +23312,7 @@
         <v>R25</v>
       </c>
       <c r="D218" t="str">
-        <v xml:space="preserve">Bontang  </v>
+        <v>Bontang</v>
       </c>
       <c r="E218" t="str">
         <v>K01</v>
@@ -23324,7 +23324,7 @@
         <v>WTP</v>
       </c>
       <c r="H218">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="219">
@@ -23338,7 +23338,7 @@
         <v>R25</v>
       </c>
       <c r="D219" t="str">
-        <v xml:space="preserve">Bontang  </v>
+        <v>Bontang</v>
       </c>
       <c r="E219" t="str">
         <v>K02</v>
@@ -23350,7 +23350,7 @@
         <v>TGH</v>
       </c>
       <c r="H219">
-        <v>161</v>
+        <v>195</v>
       </c>
     </row>
     <row r="220">
@@ -23364,7 +23364,7 @@
         <v>R25</v>
       </c>
       <c r="D220" t="str">
-        <v xml:space="preserve">Bontang  </v>
+        <v>Bontang</v>
       </c>
       <c r="E220" t="str">
         <v>K03</v>
@@ -23376,7 +23376,7 @@
         <v>TSD</v>
       </c>
       <c r="H220">
-        <v>3636</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="221">
@@ -23390,7 +23390,7 @@
         <v>R25</v>
       </c>
       <c r="D221" t="str">
-        <v xml:space="preserve">Bontang  </v>
+        <v>Bontang</v>
       </c>
       <c r="E221" t="str">
         <v>K04</v>
@@ -23402,7 +23402,7 @@
         <v>TGH</v>
       </c>
       <c r="H221">
-        <v>104</v>
+        <v>240</v>
       </c>
     </row>
     <row r="222">
@@ -23416,7 +23416,7 @@
         <v>R25</v>
       </c>
       <c r="D222" t="str">
-        <v xml:space="preserve">Bontang  </v>
+        <v>Bontang</v>
       </c>
       <c r="E222" t="str">
         <v>K05</v>
@@ -23428,7 +23428,7 @@
         <v>TSD</v>
       </c>
       <c r="H222">
-        <v>1593</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="223">
@@ -23442,7 +23442,7 @@
         <v>R25</v>
       </c>
       <c r="D223" t="str">
-        <v xml:space="preserve">Bontang  </v>
+        <v>Bontang</v>
       </c>
       <c r="E223" t="str">
         <v>K06</v>
@@ -23453,8 +23453,8 @@
       <c r="G223" t="str">
         <v>TGH</v>
       </c>
-      <c r="H223" t="str">
-        <v>-</v>
+      <c r="H223">
+        <v>52</v>
       </c>
     </row>
     <row r="224">
@@ -23468,7 +23468,7 @@
         <v>R25</v>
       </c>
       <c r="D224" t="str">
-        <v xml:space="preserve">Bontang  </v>
+        <v>Bontang</v>
       </c>
       <c r="E224" t="str">
         <v>K07</v>
@@ -23479,8 +23479,8 @@
       <c r="G224" t="str">
         <v>TSD</v>
       </c>
-      <c r="H224" t="str">
-        <v>-</v>
+      <c r="H224">
+        <v>940</v>
       </c>
     </row>
     <row r="225">
@@ -23494,7 +23494,7 @@
         <v>R25</v>
       </c>
       <c r="D225" t="str">
-        <v xml:space="preserve">Bontang  </v>
+        <v>Bontang</v>
       </c>
       <c r="E225" t="str">
         <v>K08</v>
@@ -23505,8 +23505,8 @@
       <c r="G225" t="str">
         <v>BSH</v>
       </c>
-      <c r="H225" t="str">
-        <v>-</v>
+      <c r="H225">
+        <v>22</v>
       </c>
     </row>
     <row r="226">
@@ -23520,7 +23520,7 @@
         <v>R25</v>
       </c>
       <c r="D226" t="str">
-        <v xml:space="preserve">Bontang  </v>
+        <v>Bontang</v>
       </c>
       <c r="E226" t="str">
         <v>K09</v>
@@ -23531,8 +23531,8 @@
       <c r="G226" t="str">
         <v>BCH</v>
       </c>
-      <c r="H226" t="str">
-        <v>-</v>
+      <c r="H226">
+        <v>17</v>
       </c>
     </row>
     <row r="227">
@@ -23558,7 +23558,7 @@
         <v>WTP</v>
       </c>
       <c r="H227">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="228">
@@ -23584,7 +23584,7 @@
         <v>TGH</v>
       </c>
       <c r="H228">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="229">
@@ -23610,7 +23610,7 @@
         <v>TSD</v>
       </c>
       <c r="H229">
-        <v>3636</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="230">
@@ -23636,7 +23636,7 @@
         <v>TGH</v>
       </c>
       <c r="H230">
-        <v>104</v>
+        <v>130</v>
       </c>
     </row>
     <row r="231">
@@ -23662,7 +23662,7 @@
         <v>TSD</v>
       </c>
       <c r="H231">
-        <v>1593</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="232">
@@ -23687,8 +23687,8 @@
       <c r="G232" t="str">
         <v>TGH</v>
       </c>
-      <c r="H232" t="str">
-        <v>-</v>
+      <c r="H232">
+        <v>46</v>
       </c>
     </row>
     <row r="233">
@@ -23713,8 +23713,8 @@
       <c r="G233" t="str">
         <v>TSD</v>
       </c>
-      <c r="H233" t="str">
-        <v>-</v>
+      <c r="H233">
+        <v>830</v>
       </c>
     </row>
     <row r="234">
@@ -23739,8 +23739,8 @@
       <c r="G234" t="str">
         <v>BSH</v>
       </c>
-      <c r="H234" t="str">
-        <v>-</v>
+      <c r="H234">
+        <v>34.8</v>
       </c>
     </row>
     <row r="235">
@@ -23765,8 +23765,8 @@
       <c r="G235" t="str">
         <v>BCH</v>
       </c>
-      <c r="H235" t="str">
-        <v>-</v>
+      <c r="H235">
+        <v>26.8</v>
       </c>
     </row>
     <row r="236">
@@ -23774,13 +23774,13 @@
         <v>2026</v>
       </c>
       <c r="B236">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C236" t="str">
-        <v>R01</v>
+        <v>R80</v>
       </c>
       <c r="D236" t="str">
-        <v>Makassar</v>
+        <v>Luwuk Tangkiang</v>
       </c>
       <c r="E236" t="str">
         <v>K01</v>
@@ -23792,12 +23792,6538 @@
         <v>WTP</v>
       </c>
       <c r="H236">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>2026</v>
+      </c>
+      <c r="B237">
+        <v>9</v>
+      </c>
+      <c r="C237" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E237" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F237" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G237" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H237">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>2026</v>
+      </c>
+      <c r="B238">
+        <v>9</v>
+      </c>
+      <c r="C238" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E238" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F238" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G238" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H238">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>2026</v>
+      </c>
+      <c r="B239">
+        <v>9</v>
+      </c>
+      <c r="C239" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E239" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F239" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G239" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H239">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>2026</v>
+      </c>
+      <c r="B240">
+        <v>9</v>
+      </c>
+      <c r="C240" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E240" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F240" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G240" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H240">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>2026</v>
+      </c>
+      <c r="B241">
+        <v>9</v>
+      </c>
+      <c r="C241" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E241" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F241" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G241" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H241">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>2026</v>
+      </c>
+      <c r="B242">
+        <v>9</v>
+      </c>
+      <c r="C242" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E242" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F242" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G242" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H242">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>2026</v>
+      </c>
+      <c r="B243">
+        <v>9</v>
+      </c>
+      <c r="C243" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E243" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F243" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G243" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H243">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>2026</v>
+      </c>
+      <c r="B244">
+        <v>9</v>
+      </c>
+      <c r="C244" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E244" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F244" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G244" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H244">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>2026</v>
+      </c>
+      <c r="B245">
+        <v>10</v>
+      </c>
+      <c r="C245" t="str">
+        <v>R01</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Makassar</v>
+      </c>
+      <c r="E245" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F245" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G245" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H245">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>2026</v>
+      </c>
+      <c r="B246">
+        <v>10</v>
+      </c>
+      <c r="C246" t="str">
+        <v>R01</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Makassar</v>
+      </c>
+      <c r="E246" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F246" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G246" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H246">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>2026</v>
+      </c>
+      <c r="B247">
+        <v>10</v>
+      </c>
+      <c r="C247" t="str">
+        <v>R01</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Makassar</v>
+      </c>
+      <c r="E247" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F247" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G247" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H247">
+        <v>3825</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>2026</v>
+      </c>
+      <c r="B248">
+        <v>10</v>
+      </c>
+      <c r="C248" t="str">
+        <v>R01</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Makassar</v>
+      </c>
+      <c r="E248" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F248" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G248" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H248">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>2026</v>
+      </c>
+      <c r="B249">
+        <v>10</v>
+      </c>
+      <c r="C249" t="str">
+        <v>R01</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Makassar</v>
+      </c>
+      <c r="E249" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F249" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G249" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H249">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>2026</v>
+      </c>
+      <c r="B250">
+        <v>10</v>
+      </c>
+      <c r="C250" t="str">
+        <v>R01</v>
+      </c>
+      <c r="D250" t="str">
+        <v>Makassar</v>
+      </c>
+      <c r="E250" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F250" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G250" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H250">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>2026</v>
+      </c>
+      <c r="B251">
+        <v>10</v>
+      </c>
+      <c r="C251" t="str">
+        <v>R01</v>
+      </c>
+      <c r="D251" t="str">
+        <v>Makassar</v>
+      </c>
+      <c r="E251" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F251" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G251" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H251">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>2026</v>
+      </c>
+      <c r="B252">
+        <v>10</v>
+      </c>
+      <c r="C252" t="str">
+        <v>R01</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Makassar</v>
+      </c>
+      <c r="E252" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F252" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G252" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H252">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>2026</v>
+      </c>
+      <c r="B253">
+        <v>10</v>
+      </c>
+      <c r="C253" t="str">
+        <v>R01</v>
+      </c>
+      <c r="D253" t="str">
+        <v>Makassar</v>
+      </c>
+      <c r="E253" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F253" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G253" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H253">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>2026</v>
+      </c>
+      <c r="B254">
+        <v>10</v>
+      </c>
+      <c r="C254" t="str">
+        <v>R02</v>
+      </c>
+      <c r="D254" t="str">
+        <v>TPK Makassar</v>
+      </c>
+      <c r="E254" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F254" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G254" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H254">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>2026</v>
+      </c>
+      <c r="B255">
+        <v>10</v>
+      </c>
+      <c r="C255" t="str">
+        <v>R02</v>
+      </c>
+      <c r="D255" t="str">
+        <v>TPK Makassar</v>
+      </c>
+      <c r="E255" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F255" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G255" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H255" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>2026</v>
+      </c>
+      <c r="B256">
+        <v>10</v>
+      </c>
+      <c r="C256" t="str">
+        <v>R02</v>
+      </c>
+      <c r="D256" t="str">
+        <v>TPK Makassar</v>
+      </c>
+      <c r="E256" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F256" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G256" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H256" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>2026</v>
+      </c>
+      <c r="B257">
+        <v>10</v>
+      </c>
+      <c r="C257" t="str">
+        <v>R02</v>
+      </c>
+      <c r="D257" t="str">
+        <v>TPK Makassar</v>
+      </c>
+      <c r="E257" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F257" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G257" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H257" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>2026</v>
+      </c>
+      <c r="B258">
+        <v>10</v>
+      </c>
+      <c r="C258" t="str">
+        <v>R02</v>
+      </c>
+      <c r="D258" t="str">
+        <v>TPK Makassar</v>
+      </c>
+      <c r="E258" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F258" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G258" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H258" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>2026</v>
+      </c>
+      <c r="B259">
+        <v>10</v>
+      </c>
+      <c r="C259" t="str">
+        <v>R02</v>
+      </c>
+      <c r="D259" t="str">
+        <v>TPK Makassar</v>
+      </c>
+      <c r="E259" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F259" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G259" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H259" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>2026</v>
+      </c>
+      <c r="B260">
+        <v>10</v>
+      </c>
+      <c r="C260" t="str">
+        <v>R02</v>
+      </c>
+      <c r="D260" t="str">
+        <v>TPK Makassar</v>
+      </c>
+      <c r="E260" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F260" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G260" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H260" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>2026</v>
+      </c>
+      <c r="B261">
+        <v>10</v>
+      </c>
+      <c r="C261" t="str">
+        <v>R02</v>
+      </c>
+      <c r="D261" t="str">
+        <v>TPK Makassar</v>
+      </c>
+      <c r="E261" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F261" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G261" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H261">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>2026</v>
+      </c>
+      <c r="B262">
+        <v>10</v>
+      </c>
+      <c r="C262" t="str">
+        <v>R02</v>
+      </c>
+      <c r="D262" t="str">
+        <v>TPK Makassar</v>
+      </c>
+      <c r="E262" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F262" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G262" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H262">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>2026</v>
+      </c>
+      <c r="B263">
+        <v>10</v>
+      </c>
+      <c r="C263" t="str">
+        <v>R03</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Samarinda</v>
+      </c>
+      <c r="E263" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F263" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G263" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H263">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>2026</v>
+      </c>
+      <c r="B264">
+        <v>10</v>
+      </c>
+      <c r="C264" t="str">
+        <v>R03</v>
+      </c>
+      <c r="D264" t="str">
+        <v>Samarinda</v>
+      </c>
+      <c r="E264" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F264" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G264" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H264">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>2026</v>
+      </c>
+      <c r="B265">
+        <v>10</v>
+      </c>
+      <c r="C265" t="str">
+        <v>R03</v>
+      </c>
+      <c r="D265" t="str">
+        <v>Samarinda</v>
+      </c>
+      <c r="E265" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F265" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G265" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H265">
+        <v>5355</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>2026</v>
+      </c>
+      <c r="B266">
+        <v>10</v>
+      </c>
+      <c r="C266" t="str">
+        <v>R03</v>
+      </c>
+      <c r="D266" t="str">
+        <v>Samarinda</v>
+      </c>
+      <c r="E266" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F266" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G266" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H266">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>2026</v>
+      </c>
+      <c r="B267">
+        <v>10</v>
+      </c>
+      <c r="C267" t="str">
+        <v>R03</v>
+      </c>
+      <c r="D267" t="str">
+        <v>Samarinda</v>
+      </c>
+      <c r="E267" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F267" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G267" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H267">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>2026</v>
+      </c>
+      <c r="B268">
+        <v>10</v>
+      </c>
+      <c r="C268" t="str">
+        <v>R03</v>
+      </c>
+      <c r="D268" t="str">
+        <v>Samarinda</v>
+      </c>
+      <c r="E268" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F268" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G268" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H268">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>2026</v>
+      </c>
+      <c r="B269">
+        <v>10</v>
+      </c>
+      <c r="C269" t="str">
+        <v>R03</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Samarinda</v>
+      </c>
+      <c r="E269" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F269" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G269" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H269">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>2026</v>
+      </c>
+      <c r="B270">
+        <v>10</v>
+      </c>
+      <c r="C270" t="str">
+        <v>R03</v>
+      </c>
+      <c r="D270" t="str">
+        <v>Samarinda</v>
+      </c>
+      <c r="E270" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F270" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G270" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H270">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>2026</v>
+      </c>
+      <c r="B271">
+        <v>10</v>
+      </c>
+      <c r="C271" t="str">
+        <v>R03</v>
+      </c>
+      <c r="D271" t="str">
+        <v>Samarinda</v>
+      </c>
+      <c r="E271" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F271" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G271" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H271">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>2026</v>
+      </c>
+      <c r="B272">
+        <v>10</v>
+      </c>
+      <c r="C272" t="str">
+        <v>R04</v>
+      </c>
+      <c r="D272" t="str">
+        <v>Balikpapan</v>
+      </c>
+      <c r="E272" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F272" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G272" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H272">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>2026</v>
+      </c>
+      <c r="B273">
+        <v>10</v>
+      </c>
+      <c r="C273" t="str">
+        <v>R04</v>
+      </c>
+      <c r="D273" t="str">
+        <v>Balikpapan</v>
+      </c>
+      <c r="E273" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F273" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G273" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H273">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>2026</v>
+      </c>
+      <c r="B274">
+        <v>10</v>
+      </c>
+      <c r="C274" t="str">
+        <v>R04</v>
+      </c>
+      <c r="D274" t="str">
+        <v>Balikpapan</v>
+      </c>
+      <c r="E274" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F274" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G274" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H274">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>2026</v>
+      </c>
+      <c r="B275">
+        <v>10</v>
+      </c>
+      <c r="C275" t="str">
+        <v>R04</v>
+      </c>
+      <c r="D275" t="str">
+        <v>Balikpapan</v>
+      </c>
+      <c r="E275" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F275" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G275" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H275">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>2026</v>
+      </c>
+      <c r="B276">
+        <v>10</v>
+      </c>
+      <c r="C276" t="str">
+        <v>R04</v>
+      </c>
+      <c r="D276" t="str">
+        <v>Balikpapan</v>
+      </c>
+      <c r="E276" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F276" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G276" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H276">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>2026</v>
+      </c>
+      <c r="B277">
+        <v>10</v>
+      </c>
+      <c r="C277" t="str">
+        <v>R04</v>
+      </c>
+      <c r="D277" t="str">
+        <v>Balikpapan</v>
+      </c>
+      <c r="E277" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F277" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G277" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H277">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>2026</v>
+      </c>
+      <c r="B278">
+        <v>10</v>
+      </c>
+      <c r="C278" t="str">
+        <v>R04</v>
+      </c>
+      <c r="D278" t="str">
+        <v>Balikpapan</v>
+      </c>
+      <c r="E278" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F278" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G278" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H278">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>2026</v>
+      </c>
+      <c r="B279">
+        <v>10</v>
+      </c>
+      <c r="C279" t="str">
+        <v>R04</v>
+      </c>
+      <c r="D279" t="str">
+        <v>Balikpapan</v>
+      </c>
+      <c r="E279" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F279" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G279" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H279">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>2026</v>
+      </c>
+      <c r="B280">
+        <v>10</v>
+      </c>
+      <c r="C280" t="str">
+        <v>R04</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Balikpapan</v>
+      </c>
+      <c r="E280" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F280" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G280" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H280">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>2026</v>
+      </c>
+      <c r="B281">
+        <v>10</v>
+      </c>
+      <c r="C281" t="str">
+        <v>R05</v>
+      </c>
+      <c r="D281" t="str">
+        <v>Bitung</v>
+      </c>
+      <c r="E281" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F281" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G281" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H281">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>2026</v>
+      </c>
+      <c r="B282">
+        <v>10</v>
+      </c>
+      <c r="C282" t="str">
+        <v>R05</v>
+      </c>
+      <c r="D282" t="str">
+        <v>Bitung</v>
+      </c>
+      <c r="E282" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F282" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G282" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H282">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>2026</v>
+      </c>
+      <c r="B283">
+        <v>10</v>
+      </c>
+      <c r="C283" t="str">
+        <v>R05</v>
+      </c>
+      <c r="D283" t="str">
+        <v>Bitung</v>
+      </c>
+      <c r="E283" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F283" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G283" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H283">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>2026</v>
+      </c>
+      <c r="B284">
+        <v>10</v>
+      </c>
+      <c r="C284" t="str">
+        <v>R05</v>
+      </c>
+      <c r="D284" t="str">
+        <v>Bitung</v>
+      </c>
+      <c r="E284" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F284" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G284" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H284">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>2026</v>
+      </c>
+      <c r="B285">
+        <v>10</v>
+      </c>
+      <c r="C285" t="str">
+        <v>R05</v>
+      </c>
+      <c r="D285" t="str">
+        <v>Bitung</v>
+      </c>
+      <c r="E285" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F285" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G285" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H285">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>2026</v>
+      </c>
+      <c r="B286">
+        <v>10</v>
+      </c>
+      <c r="C286" t="str">
+        <v>R05</v>
+      </c>
+      <c r="D286" t="str">
+        <v>Bitung</v>
+      </c>
+      <c r="E286" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F286" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G286" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H286">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>2026</v>
+      </c>
+      <c r="B287">
+        <v>10</v>
+      </c>
+      <c r="C287" t="str">
+        <v>R05</v>
+      </c>
+      <c r="D287" t="str">
+        <v>Bitung</v>
+      </c>
+      <c r="E287" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F287" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G287" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H287">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>2026</v>
+      </c>
+      <c r="B288">
+        <v>10</v>
+      </c>
+      <c r="C288" t="str">
+        <v>R05</v>
+      </c>
+      <c r="D288" t="str">
+        <v>Bitung</v>
+      </c>
+      <c r="E288" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F288" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G288" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H288">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>2026</v>
+      </c>
+      <c r="B289">
+        <v>10</v>
+      </c>
+      <c r="C289" t="str">
+        <v>R05</v>
+      </c>
+      <c r="D289" t="str">
+        <v>Bitung</v>
+      </c>
+      <c r="E289" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F289" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G289" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H289">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>2026</v>
+      </c>
+      <c r="B290">
+        <v>10</v>
+      </c>
+      <c r="C290" t="str">
+        <v>R06</v>
+      </c>
+      <c r="D290" t="str">
+        <v>TPK Bitung</v>
+      </c>
+      <c r="E290" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F290" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G290" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H290">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>2026</v>
+      </c>
+      <c r="B291">
+        <v>10</v>
+      </c>
+      <c r="C291" t="str">
+        <v>R06</v>
+      </c>
+      <c r="D291" t="str">
+        <v>TPK Bitung</v>
+      </c>
+      <c r="E291" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F291" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G291" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H291" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>2026</v>
+      </c>
+      <c r="B292">
+        <v>10</v>
+      </c>
+      <c r="C292" t="str">
+        <v>R06</v>
+      </c>
+      <c r="D292" t="str">
+        <v>TPK Bitung</v>
+      </c>
+      <c r="E292" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F292" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G292" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H292" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>2026</v>
+      </c>
+      <c r="B293">
+        <v>10</v>
+      </c>
+      <c r="C293" t="str">
+        <v>R06</v>
+      </c>
+      <c r="D293" t="str">
+        <v>TPK Bitung</v>
+      </c>
+      <c r="E293" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F293" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G293" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H293" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>2026</v>
+      </c>
+      <c r="B294">
+        <v>10</v>
+      </c>
+      <c r="C294" t="str">
+        <v>R06</v>
+      </c>
+      <c r="D294" t="str">
+        <v>TPK Bitung</v>
+      </c>
+      <c r="E294" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F294" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G294" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H294" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>2026</v>
+      </c>
+      <c r="B295">
+        <v>10</v>
+      </c>
+      <c r="C295" t="str">
+        <v>R06</v>
+      </c>
+      <c r="D295" t="str">
+        <v>TPK Bitung</v>
+      </c>
+      <c r="E295" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F295" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G295" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H295" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>2026</v>
+      </c>
+      <c r="B296">
+        <v>10</v>
+      </c>
+      <c r="C296" t="str">
+        <v>R06</v>
+      </c>
+      <c r="D296" t="str">
+        <v>TPK Bitung</v>
+      </c>
+      <c r="E296" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F296" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G296" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H296" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>2026</v>
+      </c>
+      <c r="B297">
+        <v>10</v>
+      </c>
+      <c r="C297" t="str">
+        <v>R06</v>
+      </c>
+      <c r="D297" t="str">
+        <v>TPK Bitung</v>
+      </c>
+      <c r="E297" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F297" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G297" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H297">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>2026</v>
+      </c>
+      <c r="B298">
+        <v>10</v>
+      </c>
+      <c r="C298" t="str">
+        <v>R06</v>
+      </c>
+      <c r="D298" t="str">
+        <v>TPK Bitung</v>
+      </c>
+      <c r="E298" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F298" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G298" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H298">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>2026</v>
+      </c>
+      <c r="B299">
+        <v>10</v>
+      </c>
+      <c r="C299" t="str">
+        <v>R07</v>
+      </c>
+      <c r="D299" t="str">
+        <v>Ambon</v>
+      </c>
+      <c r="E299" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F299" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G299" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H299">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>2026</v>
+      </c>
+      <c r="B300">
+        <v>10</v>
+      </c>
+      <c r="C300" t="str">
+        <v>R07</v>
+      </c>
+      <c r="D300" t="str">
+        <v>Ambon</v>
+      </c>
+      <c r="E300" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F300" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G300" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H300">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>2026</v>
+      </c>
+      <c r="B301">
+        <v>10</v>
+      </c>
+      <c r="C301" t="str">
+        <v>R07</v>
+      </c>
+      <c r="D301" t="str">
+        <v>Ambon</v>
+      </c>
+      <c r="E301" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F301" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G301" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H301">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>2026</v>
+      </c>
+      <c r="B302">
+        <v>10</v>
+      </c>
+      <c r="C302" t="str">
+        <v>R07</v>
+      </c>
+      <c r="D302" t="str">
+        <v>Ambon</v>
+      </c>
+      <c r="E302" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F302" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G302" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H302">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>2026</v>
+      </c>
+      <c r="B303">
+        <v>10</v>
+      </c>
+      <c r="C303" t="str">
+        <v>R07</v>
+      </c>
+      <c r="D303" t="str">
+        <v>Ambon</v>
+      </c>
+      <c r="E303" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F303" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G303" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H303">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>2026</v>
+      </c>
+      <c r="B304">
+        <v>10</v>
+      </c>
+      <c r="C304" t="str">
+        <v>R07</v>
+      </c>
+      <c r="D304" t="str">
+        <v>Ambon</v>
+      </c>
+      <c r="E304" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F304" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G304" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H304">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>2026</v>
+      </c>
+      <c r="B305">
+        <v>10</v>
+      </c>
+      <c r="C305" t="str">
+        <v>R07</v>
+      </c>
+      <c r="D305" t="str">
+        <v>Ambon</v>
+      </c>
+      <c r="E305" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F305" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G305" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H305">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>2026</v>
+      </c>
+      <c r="B306">
+        <v>10</v>
+      </c>
+      <c r="C306" t="str">
+        <v>R07</v>
+      </c>
+      <c r="D306" t="str">
+        <v>Ambon</v>
+      </c>
+      <c r="E306" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F306" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G306" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H306">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>2026</v>
+      </c>
+      <c r="B307">
+        <v>10</v>
+      </c>
+      <c r="C307" t="str">
+        <v>R07</v>
+      </c>
+      <c r="D307" t="str">
+        <v>Ambon</v>
+      </c>
+      <c r="E307" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F307" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G307" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H307">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>2026</v>
+      </c>
+      <c r="B308">
+        <v>10</v>
+      </c>
+      <c r="C308" t="str">
+        <v>R08</v>
+      </c>
+      <c r="D308" t="str">
+        <v>Sorong</v>
+      </c>
+      <c r="E308" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F308" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G308" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H308">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>2026</v>
+      </c>
+      <c r="B309">
+        <v>10</v>
+      </c>
+      <c r="C309" t="str">
+        <v>R08</v>
+      </c>
+      <c r="D309" t="str">
+        <v>Sorong</v>
+      </c>
+      <c r="E309" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F309" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G309" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H309">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>2026</v>
+      </c>
+      <c r="B310">
+        <v>10</v>
+      </c>
+      <c r="C310" t="str">
+        <v>R08</v>
+      </c>
+      <c r="D310" t="str">
+        <v>Sorong</v>
+      </c>
+      <c r="E310" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F310" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G310" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H310">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>2026</v>
+      </c>
+      <c r="B311">
+        <v>10</v>
+      </c>
+      <c r="C311" t="str">
+        <v>R08</v>
+      </c>
+      <c r="D311" t="str">
+        <v>Sorong</v>
+      </c>
+      <c r="E311" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F311" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G311" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H311">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>2026</v>
+      </c>
+      <c r="B312">
+        <v>10</v>
+      </c>
+      <c r="C312" t="str">
+        <v>R08</v>
+      </c>
+      <c r="D312" t="str">
+        <v>Sorong</v>
+      </c>
+      <c r="E312" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F312" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G312" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H312">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>2026</v>
+      </c>
+      <c r="B313">
+        <v>10</v>
+      </c>
+      <c r="C313" t="str">
+        <v>R08</v>
+      </c>
+      <c r="D313" t="str">
+        <v>Sorong</v>
+      </c>
+      <c r="E313" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F313" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G313" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H313">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>2026</v>
+      </c>
+      <c r="B314">
+        <v>10</v>
+      </c>
+      <c r="C314" t="str">
+        <v>R08</v>
+      </c>
+      <c r="D314" t="str">
+        <v>Sorong</v>
+      </c>
+      <c r="E314" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F314" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G314" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H314">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>2026</v>
+      </c>
+      <c r="B315">
+        <v>10</v>
+      </c>
+      <c r="C315" t="str">
+        <v>R08</v>
+      </c>
+      <c r="D315" t="str">
+        <v>Sorong</v>
+      </c>
+      <c r="E315" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F315" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G315" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H315">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>2026</v>
+      </c>
+      <c r="B316">
+        <v>10</v>
+      </c>
+      <c r="C316" t="str">
+        <v>R08</v>
+      </c>
+      <c r="D316" t="str">
+        <v>Sorong</v>
+      </c>
+      <c r="E316" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F316" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G316" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H316">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>2026</v>
+      </c>
+      <c r="B317">
+        <v>10</v>
+      </c>
+      <c r="C317" t="str">
+        <v>R09</v>
+      </c>
+      <c r="D317" t="str">
+        <v>Jayapura</v>
+      </c>
+      <c r="E317" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F317" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G317" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H317">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>2026</v>
+      </c>
+      <c r="B318">
+        <v>10</v>
+      </c>
+      <c r="C318" t="str">
+        <v>R09</v>
+      </c>
+      <c r="D318" t="str">
+        <v>Jayapura</v>
+      </c>
+      <c r="E318" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F318" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G318" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H318">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>2026</v>
+      </c>
+      <c r="B319">
+        <v>10</v>
+      </c>
+      <c r="C319" t="str">
+        <v>R09</v>
+      </c>
+      <c r="D319" t="str">
+        <v>Jayapura</v>
+      </c>
+      <c r="E319" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F319" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G319" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H319">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>2026</v>
+      </c>
+      <c r="B320">
+        <v>10</v>
+      </c>
+      <c r="C320" t="str">
+        <v>R09</v>
+      </c>
+      <c r="D320" t="str">
+        <v>Jayapura</v>
+      </c>
+      <c r="E320" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F320" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G320" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H320">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>2026</v>
+      </c>
+      <c r="B321">
+        <v>10</v>
+      </c>
+      <c r="C321" t="str">
+        <v>R09</v>
+      </c>
+      <c r="D321" t="str">
+        <v>Jayapura</v>
+      </c>
+      <c r="E321" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F321" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G321" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H321">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>2026</v>
+      </c>
+      <c r="B322">
+        <v>10</v>
+      </c>
+      <c r="C322" t="str">
+        <v>R09</v>
+      </c>
+      <c r="D322" t="str">
+        <v>Jayapura</v>
+      </c>
+      <c r="E322" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F322" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G322" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H322">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>2026</v>
+      </c>
+      <c r="B323">
+        <v>10</v>
+      </c>
+      <c r="C323" t="str">
+        <v>R09</v>
+      </c>
+      <c r="D323" t="str">
+        <v>Jayapura</v>
+      </c>
+      <c r="E323" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F323" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G323" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H323">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>2026</v>
+      </c>
+      <c r="B324">
+        <v>10</v>
+      </c>
+      <c r="C324" t="str">
+        <v>R09</v>
+      </c>
+      <c r="D324" t="str">
+        <v>Jayapura</v>
+      </c>
+      <c r="E324" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F324" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G324" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H324">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>2026</v>
+      </c>
+      <c r="B325">
+        <v>10</v>
+      </c>
+      <c r="C325" t="str">
+        <v>R09</v>
+      </c>
+      <c r="D325" t="str">
+        <v>Jayapura</v>
+      </c>
+      <c r="E325" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F325" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G325" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H325">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>2026</v>
+      </c>
+      <c r="B326">
+        <v>10</v>
+      </c>
+      <c r="C326" t="str">
+        <v>R10</v>
+      </c>
+      <c r="D326" t="str">
+        <v>Tarakan</v>
+      </c>
+      <c r="E326" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F326" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G326" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H326">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>2026</v>
+      </c>
+      <c r="B327">
+        <v>10</v>
+      </c>
+      <c r="C327" t="str">
+        <v>R10</v>
+      </c>
+      <c r="D327" t="str">
+        <v>Tarakan</v>
+      </c>
+      <c r="E327" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F327" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G327" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H327">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>2026</v>
+      </c>
+      <c r="B328">
+        <v>10</v>
+      </c>
+      <c r="C328" t="str">
+        <v>R10</v>
+      </c>
+      <c r="D328" t="str">
+        <v>Tarakan</v>
+      </c>
+      <c r="E328" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F328" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G328" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H328">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>2026</v>
+      </c>
+      <c r="B329">
+        <v>10</v>
+      </c>
+      <c r="C329" t="str">
+        <v>R10</v>
+      </c>
+      <c r="D329" t="str">
+        <v>Tarakan</v>
+      </c>
+      <c r="E329" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F329" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G329" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H329">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>2026</v>
+      </c>
+      <c r="B330">
+        <v>10</v>
+      </c>
+      <c r="C330" t="str">
+        <v>R10</v>
+      </c>
+      <c r="D330" t="str">
+        <v>Tarakan</v>
+      </c>
+      <c r="E330" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F330" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G330" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H330">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>2026</v>
+      </c>
+      <c r="B331">
+        <v>10</v>
+      </c>
+      <c r="C331" t="str">
+        <v>R10</v>
+      </c>
+      <c r="D331" t="str">
+        <v>Tarakan</v>
+      </c>
+      <c r="E331" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F331" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G331" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H331">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>2026</v>
+      </c>
+      <c r="B332">
+        <v>10</v>
+      </c>
+      <c r="C332" t="str">
+        <v>R10</v>
+      </c>
+      <c r="D332" t="str">
+        <v>Tarakan</v>
+      </c>
+      <c r="E332" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F332" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G332" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H332">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>2026</v>
+      </c>
+      <c r="B333">
+        <v>10</v>
+      </c>
+      <c r="C333" t="str">
+        <v>R10</v>
+      </c>
+      <c r="D333" t="str">
+        <v>Tarakan</v>
+      </c>
+      <c r="E333" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F333" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G333" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H333">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>2026</v>
+      </c>
+      <c r="B334">
+        <v>10</v>
+      </c>
+      <c r="C334" t="str">
+        <v>R10</v>
+      </c>
+      <c r="D334" t="str">
+        <v>Tarakan</v>
+      </c>
+      <c r="E334" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F334" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G334" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H334">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>2026</v>
+      </c>
+      <c r="B335">
+        <v>10</v>
+      </c>
+      <c r="C335" t="str">
+        <v>R11</v>
+      </c>
+      <c r="D335" t="str">
+        <v>Pantoloan</v>
+      </c>
+      <c r="E335" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F335" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G335" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H335">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>2026</v>
+      </c>
+      <c r="B336">
+        <v>10</v>
+      </c>
+      <c r="C336" t="str">
+        <v>R11</v>
+      </c>
+      <c r="D336" t="str">
+        <v>Pantoloan</v>
+      </c>
+      <c r="E336" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F336" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G336" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H336">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>2026</v>
+      </c>
+      <c r="B337">
+        <v>10</v>
+      </c>
+      <c r="C337" t="str">
+        <v>R11</v>
+      </c>
+      <c r="D337" t="str">
+        <v>Pantoloan</v>
+      </c>
+      <c r="E337" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F337" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G337" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H337">
+        <v>3315</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>2026</v>
+      </c>
+      <c r="B338">
+        <v>10</v>
+      </c>
+      <c r="C338" t="str">
+        <v>R11</v>
+      </c>
+      <c r="D338" t="str">
+        <v>Pantoloan</v>
+      </c>
+      <c r="E338" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F338" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G338" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H338">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>2026</v>
+      </c>
+      <c r="B339">
+        <v>10</v>
+      </c>
+      <c r="C339" t="str">
+        <v>R11</v>
+      </c>
+      <c r="D339" t="str">
+        <v>Pantoloan</v>
+      </c>
+      <c r="E339" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F339" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G339" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H339">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>2026</v>
+      </c>
+      <c r="B340">
+        <v>10</v>
+      </c>
+      <c r="C340" t="str">
+        <v>R11</v>
+      </c>
+      <c r="D340" t="str">
+        <v>Pantoloan</v>
+      </c>
+      <c r="E340" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F340" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G340" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H340">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>2026</v>
+      </c>
+      <c r="B341">
+        <v>10</v>
+      </c>
+      <c r="C341" t="str">
+        <v>R11</v>
+      </c>
+      <c r="D341" t="str">
+        <v>Pantoloan</v>
+      </c>
+      <c r="E341" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F341" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G341" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H341">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>2026</v>
+      </c>
+      <c r="B342">
+        <v>10</v>
+      </c>
+      <c r="C342" t="str">
+        <v>R11</v>
+      </c>
+      <c r="D342" t="str">
+        <v>Pantoloan</v>
+      </c>
+      <c r="E342" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F342" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G342" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H342">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>2026</v>
+      </c>
+      <c r="B343">
+        <v>10</v>
+      </c>
+      <c r="C343" t="str">
+        <v>R11</v>
+      </c>
+      <c r="D343" t="str">
+        <v>Pantoloan</v>
+      </c>
+      <c r="E343" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F343" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G343" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H343">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>2026</v>
+      </c>
+      <c r="B344">
+        <v>10</v>
+      </c>
+      <c r="C344" t="str">
+        <v>R12</v>
+      </c>
+      <c r="D344" t="str">
+        <v>Ternate</v>
+      </c>
+      <c r="E344" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F344" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G344" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H344">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>2026</v>
+      </c>
+      <c r="B345">
+        <v>10</v>
+      </c>
+      <c r="C345" t="str">
+        <v>R12</v>
+      </c>
+      <c r="D345" t="str">
+        <v>Ternate</v>
+      </c>
+      <c r="E345" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F345" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G345" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H345">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>2026</v>
+      </c>
+      <c r="B346">
+        <v>10</v>
+      </c>
+      <c r="C346" t="str">
+        <v>R12</v>
+      </c>
+      <c r="D346" t="str">
+        <v>Ternate</v>
+      </c>
+      <c r="E346" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F346" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G346" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H346">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>2026</v>
+      </c>
+      <c r="B347">
+        <v>10</v>
+      </c>
+      <c r="C347" t="str">
+        <v>R12</v>
+      </c>
+      <c r="D347" t="str">
+        <v>Ternate</v>
+      </c>
+      <c r="E347" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F347" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G347" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H347">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>2026</v>
+      </c>
+      <c r="B348">
+        <v>10</v>
+      </c>
+      <c r="C348" t="str">
+        <v>R12</v>
+      </c>
+      <c r="D348" t="str">
+        <v>Ternate</v>
+      </c>
+      <c r="E348" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F348" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G348" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H348">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>2026</v>
+      </c>
+      <c r="B349">
+        <v>10</v>
+      </c>
+      <c r="C349" t="str">
+        <v>R12</v>
+      </c>
+      <c r="D349" t="str">
+        <v>Ternate</v>
+      </c>
+      <c r="E349" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F349" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G349" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H349">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>2026</v>
+      </c>
+      <c r="B350">
+        <v>10</v>
+      </c>
+      <c r="C350" t="str">
+        <v>R12</v>
+      </c>
+      <c r="D350" t="str">
+        <v>Ternate</v>
+      </c>
+      <c r="E350" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F350" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G350" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H350">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>2026</v>
+      </c>
+      <c r="B351">
+        <v>10</v>
+      </c>
+      <c r="C351" t="str">
+        <v>R12</v>
+      </c>
+      <c r="D351" t="str">
+        <v>Ternate</v>
+      </c>
+      <c r="E351" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F351" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G351" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H351">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>2026</v>
+      </c>
+      <c r="B352">
+        <v>10</v>
+      </c>
+      <c r="C352" t="str">
+        <v>R12</v>
+      </c>
+      <c r="D352" t="str">
+        <v>Ternate</v>
+      </c>
+      <c r="E352" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F352" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G352" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H352">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>2026</v>
+      </c>
+      <c r="B353">
+        <v>10</v>
+      </c>
+      <c r="C353" t="str">
+        <v>R13</v>
+      </c>
+      <c r="D353" t="str">
+        <v>Kendari</v>
+      </c>
+      <c r="E353" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F353" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G353" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H353">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>2026</v>
+      </c>
+      <c r="B354">
+        <v>10</v>
+      </c>
+      <c r="C354" t="str">
+        <v>R13</v>
+      </c>
+      <c r="D354" t="str">
+        <v>Kendari</v>
+      </c>
+      <c r="E354" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F354" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G354" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H354">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>2026</v>
+      </c>
+      <c r="B355">
+        <v>10</v>
+      </c>
+      <c r="C355" t="str">
+        <v>R13</v>
+      </c>
+      <c r="D355" t="str">
+        <v>Kendari</v>
+      </c>
+      <c r="E355" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F355" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G355" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H355">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>2026</v>
+      </c>
+      <c r="B356">
+        <v>10</v>
+      </c>
+      <c r="C356" t="str">
+        <v>R13</v>
+      </c>
+      <c r="D356" t="str">
+        <v>Kendari</v>
+      </c>
+      <c r="E356" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F356" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G356" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H356">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>2026</v>
+      </c>
+      <c r="B357">
+        <v>10</v>
+      </c>
+      <c r="C357" t="str">
+        <v>R13</v>
+      </c>
+      <c r="D357" t="str">
+        <v>Kendari</v>
+      </c>
+      <c r="E357" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F357" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G357" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H357">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>2026</v>
+      </c>
+      <c r="B358">
+        <v>10</v>
+      </c>
+      <c r="C358" t="str">
+        <v>R13</v>
+      </c>
+      <c r="D358" t="str">
+        <v>Kendari</v>
+      </c>
+      <c r="E358" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F358" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G358" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H358">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>2026</v>
+      </c>
+      <c r="B359">
+        <v>10</v>
+      </c>
+      <c r="C359" t="str">
+        <v>R13</v>
+      </c>
+      <c r="D359" t="str">
+        <v>Kendari</v>
+      </c>
+      <c r="E359" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F359" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G359" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H359">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>2026</v>
+      </c>
+      <c r="B360">
+        <v>10</v>
+      </c>
+      <c r="C360" t="str">
+        <v>R13</v>
+      </c>
+      <c r="D360" t="str">
+        <v>Kendari</v>
+      </c>
+      <c r="E360" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F360" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G360" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H360">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>2026</v>
+      </c>
+      <c r="B361">
+        <v>10</v>
+      </c>
+      <c r="C361" t="str">
+        <v>R13</v>
+      </c>
+      <c r="D361" t="str">
+        <v>Kendari</v>
+      </c>
+      <c r="E361" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F361" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G361" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H361">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>2026</v>
+      </c>
+      <c r="B362">
+        <v>10</v>
+      </c>
+      <c r="C362" t="str">
+        <v>R14</v>
+      </c>
+      <c r="D362" t="str">
+        <v>Parepare</v>
+      </c>
+      <c r="E362" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F362" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G362" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H362">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>2026</v>
+      </c>
+      <c r="B363">
+        <v>10</v>
+      </c>
+      <c r="C363" t="str">
+        <v>R14</v>
+      </c>
+      <c r="D363" t="str">
+        <v>Parepare</v>
+      </c>
+      <c r="E363" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F363" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G363" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H363">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>2026</v>
+      </c>
+      <c r="B364">
+        <v>10</v>
+      </c>
+      <c r="C364" t="str">
+        <v>R14</v>
+      </c>
+      <c r="D364" t="str">
+        <v>Parepare</v>
+      </c>
+      <c r="E364" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F364" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G364" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H364">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>2026</v>
+      </c>
+      <c r="B365">
+        <v>10</v>
+      </c>
+      <c r="C365" t="str">
+        <v>R14</v>
+      </c>
+      <c r="D365" t="str">
+        <v>Parepare</v>
+      </c>
+      <c r="E365" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F365" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G365" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H365">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>2026</v>
+      </c>
+      <c r="B366">
+        <v>10</v>
+      </c>
+      <c r="C366" t="str">
+        <v>R14</v>
+      </c>
+      <c r="D366" t="str">
+        <v>Parepare</v>
+      </c>
+      <c r="E366" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F366" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G366" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H366">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>2026</v>
+      </c>
+      <c r="B367">
+        <v>10</v>
+      </c>
+      <c r="C367" t="str">
+        <v>R14</v>
+      </c>
+      <c r="D367" t="str">
+        <v>Parepare</v>
+      </c>
+      <c r="E367" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F367" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G367" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H367">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>2026</v>
+      </c>
+      <c r="B368">
+        <v>10</v>
+      </c>
+      <c r="C368" t="str">
+        <v>R14</v>
+      </c>
+      <c r="D368" t="str">
+        <v>Parepare</v>
+      </c>
+      <c r="E368" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F368" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G368" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H368">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>2026</v>
+      </c>
+      <c r="B369">
+        <v>10</v>
+      </c>
+      <c r="C369" t="str">
+        <v>R14</v>
+      </c>
+      <c r="D369" t="str">
+        <v>Parepare</v>
+      </c>
+      <c r="E369" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F369" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G369" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H369">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>2026</v>
+      </c>
+      <c r="B370">
+        <v>10</v>
+      </c>
+      <c r="C370" t="str">
+        <v>R14</v>
+      </c>
+      <c r="D370" t="str">
+        <v>Parepare</v>
+      </c>
+      <c r="E370" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F370" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G370" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H370">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>2026</v>
+      </c>
+      <c r="B371">
+        <v>10</v>
+      </c>
+      <c r="C371" t="str">
+        <v>R15</v>
+      </c>
+      <c r="D371" t="str">
+        <v>Biak</v>
+      </c>
+      <c r="E371" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F371" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G371" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H371">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>2026</v>
+      </c>
+      <c r="B372">
+        <v>10</v>
+      </c>
+      <c r="C372" t="str">
+        <v>R15</v>
+      </c>
+      <c r="D372" t="str">
+        <v>Biak</v>
+      </c>
+      <c r="E372" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F372" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G372" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H372">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>2026</v>
+      </c>
+      <c r="B373">
+        <v>10</v>
+      </c>
+      <c r="C373" t="str">
+        <v>R15</v>
+      </c>
+      <c r="D373" t="str">
+        <v>Biak</v>
+      </c>
+      <c r="E373" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F373" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G373" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H373">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <v>2026</v>
+      </c>
+      <c r="B374">
+        <v>10</v>
+      </c>
+      <c r="C374" t="str">
+        <v>R15</v>
+      </c>
+      <c r="D374" t="str">
+        <v>Biak</v>
+      </c>
+      <c r="E374" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F374" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G374" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H374">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375">
+        <v>2026</v>
+      </c>
+      <c r="B375">
+        <v>10</v>
+      </c>
+      <c r="C375" t="str">
+        <v>R15</v>
+      </c>
+      <c r="D375" t="str">
+        <v>Biak</v>
+      </c>
+      <c r="E375" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F375" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G375" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H375">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376">
+        <v>2026</v>
+      </c>
+      <c r="B376">
+        <v>10</v>
+      </c>
+      <c r="C376" t="str">
+        <v>R15</v>
+      </c>
+      <c r="D376" t="str">
+        <v>Biak</v>
+      </c>
+      <c r="E376" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F376" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G376" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H376">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377">
+        <v>2026</v>
+      </c>
+      <c r="B377">
+        <v>10</v>
+      </c>
+      <c r="C377" t="str">
+        <v>R15</v>
+      </c>
+      <c r="D377" t="str">
+        <v>Biak</v>
+      </c>
+      <c r="E377" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F377" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G377" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H377">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <v>2026</v>
+      </c>
+      <c r="B378">
+        <v>10</v>
+      </c>
+      <c r="C378" t="str">
+        <v>R15</v>
+      </c>
+      <c r="D378" t="str">
+        <v>Biak</v>
+      </c>
+      <c r="E378" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F378" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G378" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H378">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>2026</v>
+      </c>
+      <c r="B379">
+        <v>10</v>
+      </c>
+      <c r="C379" t="str">
+        <v>R15</v>
+      </c>
+      <c r="D379" t="str">
+        <v>Biak</v>
+      </c>
+      <c r="E379" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F379" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G379" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H379">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>2026</v>
+      </c>
+      <c r="B380">
+        <v>10</v>
+      </c>
+      <c r="C380" t="str">
+        <v>R16</v>
+      </c>
+      <c r="D380" t="str">
+        <v>Merauke</v>
+      </c>
+      <c r="E380" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F380" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G380" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H380">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <v>2026</v>
+      </c>
+      <c r="B381">
+        <v>10</v>
+      </c>
+      <c r="C381" t="str">
+        <v>R16</v>
+      </c>
+      <c r="D381" t="str">
+        <v>Merauke</v>
+      </c>
+      <c r="E381" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F381" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G381" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H381">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382">
+        <v>2026</v>
+      </c>
+      <c r="B382">
+        <v>10</v>
+      </c>
+      <c r="C382" t="str">
+        <v>R16</v>
+      </c>
+      <c r="D382" t="str">
+        <v>Merauke</v>
+      </c>
+      <c r="E382" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F382" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G382" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H382">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383">
+        <v>2026</v>
+      </c>
+      <c r="B383">
+        <v>10</v>
+      </c>
+      <c r="C383" t="str">
+        <v>R16</v>
+      </c>
+      <c r="D383" t="str">
+        <v>Merauke</v>
+      </c>
+      <c r="E383" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F383" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G383" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H383">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384">
+        <v>2026</v>
+      </c>
+      <c r="B384">
+        <v>10</v>
+      </c>
+      <c r="C384" t="str">
+        <v>R16</v>
+      </c>
+      <c r="D384" t="str">
+        <v>Merauke</v>
+      </c>
+      <c r="E384" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F384" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G384" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H384">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385">
+        <v>2026</v>
+      </c>
+      <c r="B385">
+        <v>10</v>
+      </c>
+      <c r="C385" t="str">
+        <v>R16</v>
+      </c>
+      <c r="D385" t="str">
+        <v>Merauke</v>
+      </c>
+      <c r="E385" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F385" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G385" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H385">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386">
+        <v>2026</v>
+      </c>
+      <c r="B386">
+        <v>10</v>
+      </c>
+      <c r="C386" t="str">
+        <v>R16</v>
+      </c>
+      <c r="D386" t="str">
+        <v>Merauke</v>
+      </c>
+      <c r="E386" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F386" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G386" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H386">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387">
+        <v>2026</v>
+      </c>
+      <c r="B387">
+        <v>10</v>
+      </c>
+      <c r="C387" t="str">
+        <v>R16</v>
+      </c>
+      <c r="D387" t="str">
+        <v>Merauke</v>
+      </c>
+      <c r="E387" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F387" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G387" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H387">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388">
+        <v>2026</v>
+      </c>
+      <c r="B388">
+        <v>10</v>
+      </c>
+      <c r="C388" t="str">
+        <v>R16</v>
+      </c>
+      <c r="D388" t="str">
+        <v>Merauke</v>
+      </c>
+      <c r="E388" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F388" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G388" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H388">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389">
+        <v>2026</v>
+      </c>
+      <c r="B389">
+        <v>10</v>
+      </c>
+      <c r="C389" t="str">
+        <v>R17</v>
+      </c>
+      <c r="D389" t="str">
+        <v>Manokwari</v>
+      </c>
+      <c r="E389" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F389" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G389" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H389">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390">
+        <v>2026</v>
+      </c>
+      <c r="B390">
+        <v>10</v>
+      </c>
+      <c r="C390" t="str">
+        <v>R17</v>
+      </c>
+      <c r="D390" t="str">
+        <v>Manokwari</v>
+      </c>
+      <c r="E390" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F390" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G390" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H390">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391">
+        <v>2026</v>
+      </c>
+      <c r="B391">
+        <v>10</v>
+      </c>
+      <c r="C391" t="str">
+        <v>R17</v>
+      </c>
+      <c r="D391" t="str">
+        <v>Manokwari</v>
+      </c>
+      <c r="E391" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F391" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G391" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H391">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392">
+        <v>2026</v>
+      </c>
+      <c r="B392">
+        <v>10</v>
+      </c>
+      <c r="C392" t="str">
+        <v>R17</v>
+      </c>
+      <c r="D392" t="str">
+        <v>Manokwari</v>
+      </c>
+      <c r="E392" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F392" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G392" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H392">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393">
+        <v>2026</v>
+      </c>
+      <c r="B393">
+        <v>10</v>
+      </c>
+      <c r="C393" t="str">
+        <v>R17</v>
+      </c>
+      <c r="D393" t="str">
+        <v>Manokwari</v>
+      </c>
+      <c r="E393" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F393" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G393" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H393">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394">
+        <v>2026</v>
+      </c>
+      <c r="B394">
+        <v>10</v>
+      </c>
+      <c r="C394" t="str">
+        <v>R17</v>
+      </c>
+      <c r="D394" t="str">
+        <v>Manokwari</v>
+      </c>
+      <c r="E394" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F394" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G394" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H394">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395">
+        <v>2026</v>
+      </c>
+      <c r="B395">
+        <v>10</v>
+      </c>
+      <c r="C395" t="str">
+        <v>R17</v>
+      </c>
+      <c r="D395" t="str">
+        <v>Manokwari</v>
+      </c>
+      <c r="E395" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F395" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G395" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H395">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396">
+        <v>2026</v>
+      </c>
+      <c r="B396">
+        <v>10</v>
+      </c>
+      <c r="C396" t="str">
+        <v>R17</v>
+      </c>
+      <c r="D396" t="str">
+        <v>Manokwari</v>
+      </c>
+      <c r="E396" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F396" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G396" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H396">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397">
+        <v>2026</v>
+      </c>
+      <c r="B397">
+        <v>10</v>
+      </c>
+      <c r="C397" t="str">
+        <v>R17</v>
+      </c>
+      <c r="D397" t="str">
+        <v>Manokwari</v>
+      </c>
+      <c r="E397" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F397" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G397" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H397">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398">
+        <v>2026</v>
+      </c>
+      <c r="B398">
+        <v>10</v>
+      </c>
+      <c r="C398" t="str">
+        <v>R18</v>
+      </c>
+      <c r="D398" t="str">
+        <v>Nunukan</v>
+      </c>
+      <c r="E398" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F398" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G398" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H398">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399">
+        <v>2026</v>
+      </c>
+      <c r="B399">
+        <v>10</v>
+      </c>
+      <c r="C399" t="str">
+        <v>R18</v>
+      </c>
+      <c r="D399" t="str">
+        <v>Nunukan</v>
+      </c>
+      <c r="E399" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F399" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G399" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H399">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400">
+        <v>2026</v>
+      </c>
+      <c r="B400">
+        <v>10</v>
+      </c>
+      <c r="C400" t="str">
+        <v>R18</v>
+      </c>
+      <c r="D400" t="str">
+        <v>Nunukan</v>
+      </c>
+      <c r="E400" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F400" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G400" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H400">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401">
+        <v>2026</v>
+      </c>
+      <c r="B401">
+        <v>10</v>
+      </c>
+      <c r="C401" t="str">
+        <v>R18</v>
+      </c>
+      <c r="D401" t="str">
+        <v>Nunukan</v>
+      </c>
+      <c r="E401" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F401" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G401" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H401">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402">
+        <v>2026</v>
+      </c>
+      <c r="B402">
+        <v>10</v>
+      </c>
+      <c r="C402" t="str">
+        <v>R18</v>
+      </c>
+      <c r="D402" t="str">
+        <v>Nunukan</v>
+      </c>
+      <c r="E402" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F402" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G402" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H402">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403">
+        <v>2026</v>
+      </c>
+      <c r="B403">
+        <v>10</v>
+      </c>
+      <c r="C403" t="str">
+        <v>R18</v>
+      </c>
+      <c r="D403" t="str">
+        <v>Nunukan</v>
+      </c>
+      <c r="E403" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F403" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G403" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H403">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404">
+        <v>2026</v>
+      </c>
+      <c r="B404">
+        <v>10</v>
+      </c>
+      <c r="C404" t="str">
+        <v>R18</v>
+      </c>
+      <c r="D404" t="str">
+        <v>Nunukan</v>
+      </c>
+      <c r="E404" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F404" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G404" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H404">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405">
+        <v>2026</v>
+      </c>
+      <c r="B405">
+        <v>10</v>
+      </c>
+      <c r="C405" t="str">
+        <v>R18</v>
+      </c>
+      <c r="D405" t="str">
+        <v>Nunukan</v>
+      </c>
+      <c r="E405" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F405" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G405" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H405">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406">
+        <v>2026</v>
+      </c>
+      <c r="B406">
+        <v>10</v>
+      </c>
+      <c r="C406" t="str">
+        <v>R18</v>
+      </c>
+      <c r="D406" t="str">
+        <v>Nunukan</v>
+      </c>
+      <c r="E406" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F406" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G406" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H406">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407">
+        <v>2026</v>
+      </c>
+      <c r="B407">
+        <v>10</v>
+      </c>
+      <c r="C407" t="str">
+        <v>R19</v>
+      </c>
+      <c r="D407" t="str">
+        <v>Tg Redeb</v>
+      </c>
+      <c r="E407" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F407" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G407" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H407">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408">
+        <v>2026</v>
+      </c>
+      <c r="B408">
+        <v>10</v>
+      </c>
+      <c r="C408" t="str">
+        <v>R19</v>
+      </c>
+      <c r="D408" t="str">
+        <v>Tg Redeb</v>
+      </c>
+      <c r="E408" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F408" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G408" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H408">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409">
+        <v>2026</v>
+      </c>
+      <c r="B409">
+        <v>10</v>
+      </c>
+      <c r="C409" t="str">
+        <v>R19</v>
+      </c>
+      <c r="D409" t="str">
+        <v>Tg Redeb</v>
+      </c>
+      <c r="E409" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F409" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G409" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H409">
+        <v>6477</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410">
+        <v>2026</v>
+      </c>
+      <c r="B410">
+        <v>10</v>
+      </c>
+      <c r="C410" t="str">
+        <v>R19</v>
+      </c>
+      <c r="D410" t="str">
+        <v>Tg Redeb</v>
+      </c>
+      <c r="E410" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F410" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G410" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H410">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411">
+        <v>2026</v>
+      </c>
+      <c r="B411">
+        <v>10</v>
+      </c>
+      <c r="C411" t="str">
+        <v>R19</v>
+      </c>
+      <c r="D411" t="str">
+        <v>Tg Redeb</v>
+      </c>
+      <c r="E411" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F411" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G411" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H411">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412">
+        <v>2026</v>
+      </c>
+      <c r="B412">
+        <v>10</v>
+      </c>
+      <c r="C412" t="str">
+        <v>R19</v>
+      </c>
+      <c r="D412" t="str">
+        <v>Tg Redeb</v>
+      </c>
+      <c r="E412" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F412" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G412" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H412">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413">
+        <v>2026</v>
+      </c>
+      <c r="B413">
+        <v>10</v>
+      </c>
+      <c r="C413" t="str">
+        <v>R19</v>
+      </c>
+      <c r="D413" t="str">
+        <v>Tg Redeb</v>
+      </c>
+      <c r="E413" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F413" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G413" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H413">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414">
+        <v>2026</v>
+      </c>
+      <c r="B414">
+        <v>10</v>
+      </c>
+      <c r="C414" t="str">
+        <v>R19</v>
+      </c>
+      <c r="D414" t="str">
+        <v>Tg Redeb</v>
+      </c>
+      <c r="E414" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F414" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G414" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H414">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415">
+        <v>2026</v>
+      </c>
+      <c r="B415">
+        <v>10</v>
+      </c>
+      <c r="C415" t="str">
+        <v>R19</v>
+      </c>
+      <c r="D415" t="str">
+        <v>Tg Redeb</v>
+      </c>
+      <c r="E415" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F415" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G415" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H415">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416">
+        <v>2026</v>
+      </c>
+      <c r="B416">
+        <v>10</v>
+      </c>
+      <c r="C416" t="str">
+        <v>R20</v>
+      </c>
+      <c r="D416" t="str">
+        <v>Gorontalo</v>
+      </c>
+      <c r="E416" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F416" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G416" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H416">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417">
+        <v>2026</v>
+      </c>
+      <c r="B417">
+        <v>10</v>
+      </c>
+      <c r="C417" t="str">
+        <v>R20</v>
+      </c>
+      <c r="D417" t="str">
+        <v>Gorontalo</v>
+      </c>
+      <c r="E417" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F417" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G417" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H417">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418">
+        <v>2026</v>
+      </c>
+      <c r="B418">
+        <v>10</v>
+      </c>
+      <c r="C418" t="str">
+        <v>R20</v>
+      </c>
+      <c r="D418" t="str">
+        <v>Gorontalo</v>
+      </c>
+      <c r="E418" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F418" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G418" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H418">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419">
+        <v>2026</v>
+      </c>
+      <c r="B419">
+        <v>10</v>
+      </c>
+      <c r="C419" t="str">
+        <v>R20</v>
+      </c>
+      <c r="D419" t="str">
+        <v>Gorontalo</v>
+      </c>
+      <c r="E419" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F419" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G419" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H419">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420">
+        <v>2026</v>
+      </c>
+      <c r="B420">
+        <v>10</v>
+      </c>
+      <c r="C420" t="str">
+        <v>R20</v>
+      </c>
+      <c r="D420" t="str">
+        <v>Gorontalo</v>
+      </c>
+      <c r="E420" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F420" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G420" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H420">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421">
+        <v>2026</v>
+      </c>
+      <c r="B421">
+        <v>10</v>
+      </c>
+      <c r="C421" t="str">
+        <v>R20</v>
+      </c>
+      <c r="D421" t="str">
+        <v>Gorontalo</v>
+      </c>
+      <c r="E421" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F421" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G421" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H421">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422">
+        <v>2026</v>
+      </c>
+      <c r="B422">
+        <v>10</v>
+      </c>
+      <c r="C422" t="str">
+        <v>R20</v>
+      </c>
+      <c r="D422" t="str">
+        <v>Gorontalo</v>
+      </c>
+      <c r="E422" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F422" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G422" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H422">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423">
+        <v>2026</v>
+      </c>
+      <c r="B423">
+        <v>10</v>
+      </c>
+      <c r="C423" t="str">
+        <v>R20</v>
+      </c>
+      <c r="D423" t="str">
+        <v>Gorontalo</v>
+      </c>
+      <c r="E423" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F423" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G423" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H423">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424">
+        <v>2026</v>
+      </c>
+      <c r="B424">
+        <v>10</v>
+      </c>
+      <c r="C424" t="str">
+        <v>R20</v>
+      </c>
+      <c r="D424" t="str">
+        <v>Gorontalo</v>
+      </c>
+      <c r="E424" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F424" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G424" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H424">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425">
+        <v>2026</v>
+      </c>
+      <c r="B425">
+        <v>10</v>
+      </c>
+      <c r="C425" t="str">
+        <v>R21</v>
+      </c>
+      <c r="D425" t="str">
+        <v>Fakfak</v>
+      </c>
+      <c r="E425" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F425" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G425" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H425">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426">
+        <v>2026</v>
+      </c>
+      <c r="B426">
+        <v>10</v>
+      </c>
+      <c r="C426" t="str">
+        <v>R21</v>
+      </c>
+      <c r="D426" t="str">
+        <v>Fakfak</v>
+      </c>
+      <c r="E426" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F426" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G426" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H426">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427">
+        <v>2026</v>
+      </c>
+      <c r="B427">
+        <v>10</v>
+      </c>
+      <c r="C427" t="str">
+        <v>R21</v>
+      </c>
+      <c r="D427" t="str">
+        <v>Fakfak</v>
+      </c>
+      <c r="E427" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F427" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G427" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H427">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428">
+        <v>2026</v>
+      </c>
+      <c r="B428">
+        <v>10</v>
+      </c>
+      <c r="C428" t="str">
+        <v>R21</v>
+      </c>
+      <c r="D428" t="str">
+        <v>Fakfak</v>
+      </c>
+      <c r="E428" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F428" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G428" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H428">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429">
+        <v>2026</v>
+      </c>
+      <c r="B429">
+        <v>10</v>
+      </c>
+      <c r="C429" t="str">
+        <v>R21</v>
+      </c>
+      <c r="D429" t="str">
+        <v>Fakfak</v>
+      </c>
+      <c r="E429" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F429" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G429" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H429">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430">
+        <v>2026</v>
+      </c>
+      <c r="B430">
+        <v>10</v>
+      </c>
+      <c r="C430" t="str">
+        <v>R21</v>
+      </c>
+      <c r="D430" t="str">
+        <v>Fakfak</v>
+      </c>
+      <c r="E430" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F430" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G430" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H430">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431">
+        <v>2026</v>
+      </c>
+      <c r="B431">
+        <v>10</v>
+      </c>
+      <c r="C431" t="str">
+        <v>R21</v>
+      </c>
+      <c r="D431" t="str">
+        <v>Fakfak</v>
+      </c>
+      <c r="E431" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F431" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G431" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H431">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432">
+        <v>2026</v>
+      </c>
+      <c r="B432">
+        <v>10</v>
+      </c>
+      <c r="C432" t="str">
+        <v>R21</v>
+      </c>
+      <c r="D432" t="str">
+        <v>Fakfak</v>
+      </c>
+      <c r="E432" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F432" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G432" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H432">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433">
+        <v>2026</v>
+      </c>
+      <c r="B433">
+        <v>10</v>
+      </c>
+      <c r="C433" t="str">
+        <v>R21</v>
+      </c>
+      <c r="D433" t="str">
+        <v>Fakfak</v>
+      </c>
+      <c r="E433" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F433" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G433" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H433">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434">
+        <v>2026</v>
+      </c>
+      <c r="B434">
+        <v>10</v>
+      </c>
+      <c r="C434" t="str">
+        <v>R22</v>
+      </c>
+      <c r="D434" t="str">
+        <v>Tolitoli</v>
+      </c>
+      <c r="E434" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F434" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G434" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H434">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435">
+        <v>2026</v>
+      </c>
+      <c r="B435">
+        <v>10</v>
+      </c>
+      <c r="C435" t="str">
+        <v>R22</v>
+      </c>
+      <c r="D435" t="str">
+        <v>Tolitoli</v>
+      </c>
+      <c r="E435" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F435" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G435" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H435">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436">
+        <v>2026</v>
+      </c>
+      <c r="B436">
+        <v>10</v>
+      </c>
+      <c r="C436" t="str">
+        <v>R22</v>
+      </c>
+      <c r="D436" t="str">
+        <v>Tolitoli</v>
+      </c>
+      <c r="E436" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F436" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G436" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H436">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437">
+        <v>2026</v>
+      </c>
+      <c r="B437">
+        <v>10</v>
+      </c>
+      <c r="C437" t="str">
+        <v>R22</v>
+      </c>
+      <c r="D437" t="str">
+        <v>Tolitoli</v>
+      </c>
+      <c r="E437" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F437" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G437" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H437">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438">
+        <v>2026</v>
+      </c>
+      <c r="B438">
+        <v>10</v>
+      </c>
+      <c r="C438" t="str">
+        <v>R22</v>
+      </c>
+      <c r="D438" t="str">
+        <v>Tolitoli</v>
+      </c>
+      <c r="E438" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F438" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G438" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H438">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439">
+        <v>2026</v>
+      </c>
+      <c r="B439">
+        <v>10</v>
+      </c>
+      <c r="C439" t="str">
+        <v>R22</v>
+      </c>
+      <c r="D439" t="str">
+        <v>Tolitoli</v>
+      </c>
+      <c r="E439" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F439" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G439" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H439">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440">
+        <v>2026</v>
+      </c>
+      <c r="B440">
+        <v>10</v>
+      </c>
+      <c r="C440" t="str">
+        <v>R22</v>
+      </c>
+      <c r="D440" t="str">
+        <v>Tolitoli</v>
+      </c>
+      <c r="E440" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F440" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G440" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H440">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441">
+        <v>2026</v>
+      </c>
+      <c r="B441">
+        <v>10</v>
+      </c>
+      <c r="C441" t="str">
+        <v>R22</v>
+      </c>
+      <c r="D441" t="str">
+        <v>Tolitoli</v>
+      </c>
+      <c r="E441" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F441" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G441" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H441">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442">
+        <v>2026</v>
+      </c>
+      <c r="B442">
+        <v>10</v>
+      </c>
+      <c r="C442" t="str">
+        <v>R22</v>
+      </c>
+      <c r="D442" t="str">
+        <v>Tolitoli</v>
+      </c>
+      <c r="E442" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F442" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G442" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H442">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443">
+        <v>2026</v>
+      </c>
+      <c r="B443">
+        <v>10</v>
+      </c>
+      <c r="C443" t="str">
+        <v>R23</v>
+      </c>
+      <c r="D443" t="str">
+        <v>Manado</v>
+      </c>
+      <c r="E443" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F443" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G443" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H443">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444">
+        <v>2026</v>
+      </c>
+      <c r="B444">
+        <v>10</v>
+      </c>
+      <c r="C444" t="str">
+        <v>R23</v>
+      </c>
+      <c r="D444" t="str">
+        <v>Manado</v>
+      </c>
+      <c r="E444" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F444" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G444" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H444">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445">
+        <v>2026</v>
+      </c>
+      <c r="B445">
+        <v>10</v>
+      </c>
+      <c r="C445" t="str">
+        <v>R23</v>
+      </c>
+      <c r="D445" t="str">
+        <v>Manado</v>
+      </c>
+      <c r="E445" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F445" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G445" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H445">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446">
+        <v>2026</v>
+      </c>
+      <c r="B446">
+        <v>10</v>
+      </c>
+      <c r="C446" t="str">
+        <v>R23</v>
+      </c>
+      <c r="D446" t="str">
+        <v>Manado</v>
+      </c>
+      <c r="E446" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F446" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G446" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H446">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447">
+        <v>2026</v>
+      </c>
+      <c r="B447">
+        <v>10</v>
+      </c>
+      <c r="C447" t="str">
+        <v>R23</v>
+      </c>
+      <c r="D447" t="str">
+        <v>Manado</v>
+      </c>
+      <c r="E447" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F447" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G447" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H447">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448">
+        <v>2026</v>
+      </c>
+      <c r="B448">
+        <v>10</v>
+      </c>
+      <c r="C448" t="str">
+        <v>R23</v>
+      </c>
+      <c r="D448" t="str">
+        <v>Manado</v>
+      </c>
+      <c r="E448" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F448" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G448" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H448">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449">
+        <v>2026</v>
+      </c>
+      <c r="B449">
+        <v>10</v>
+      </c>
+      <c r="C449" t="str">
+        <v>R23</v>
+      </c>
+      <c r="D449" t="str">
+        <v>Manado</v>
+      </c>
+      <c r="E449" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F449" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G449" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H449">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450">
+        <v>2026</v>
+      </c>
+      <c r="B450">
+        <v>10</v>
+      </c>
+      <c r="C450" t="str">
+        <v>R23</v>
+      </c>
+      <c r="D450" t="str">
+        <v>Manado</v>
+      </c>
+      <c r="E450" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F450" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G450" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H450">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451">
+        <v>2026</v>
+      </c>
+      <c r="B451">
+        <v>10</v>
+      </c>
+      <c r="C451" t="str">
+        <v>R23</v>
+      </c>
+      <c r="D451" t="str">
+        <v>Manado</v>
+      </c>
+      <c r="E451" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F451" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G451" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H451">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452">
+        <v>2026</v>
+      </c>
+      <c r="B452">
+        <v>10</v>
+      </c>
+      <c r="C452" t="str">
+        <v>R24</v>
+      </c>
+      <c r="D452" t="str">
+        <v>Makassar New Port</v>
+      </c>
+      <c r="E452" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F452" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G452" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H452">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453">
+        <v>2026</v>
+      </c>
+      <c r="B453">
+        <v>10</v>
+      </c>
+      <c r="C453" t="str">
+        <v>R24</v>
+      </c>
+      <c r="D453" t="str">
+        <v>Makassar New Port</v>
+      </c>
+      <c r="E453" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F453" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G453" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H453" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454">
+        <v>2026</v>
+      </c>
+      <c r="B454">
+        <v>10</v>
+      </c>
+      <c r="C454" t="str">
+        <v>R24</v>
+      </c>
+      <c r="D454" t="str">
+        <v>Makassar New Port</v>
+      </c>
+      <c r="E454" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F454" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G454" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H454" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455">
+        <v>2026</v>
+      </c>
+      <c r="B455">
+        <v>10</v>
+      </c>
+      <c r="C455" t="str">
+        <v>R24</v>
+      </c>
+      <c r="D455" t="str">
+        <v>Makassar New Port</v>
+      </c>
+      <c r="E455" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F455" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G455" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H455" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456">
+        <v>2026</v>
+      </c>
+      <c r="B456">
+        <v>10</v>
+      </c>
+      <c r="C456" t="str">
+        <v>R24</v>
+      </c>
+      <c r="D456" t="str">
+        <v>Makassar New Port</v>
+      </c>
+      <c r="E456" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F456" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G456" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H456" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457">
+        <v>2026</v>
+      </c>
+      <c r="B457">
+        <v>10</v>
+      </c>
+      <c r="C457" t="str">
+        <v>R24</v>
+      </c>
+      <c r="D457" t="str">
+        <v>Makassar New Port</v>
+      </c>
+      <c r="E457" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F457" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G457" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H457" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458">
+        <v>2026</v>
+      </c>
+      <c r="B458">
+        <v>10</v>
+      </c>
+      <c r="C458" t="str">
+        <v>R24</v>
+      </c>
+      <c r="D458" t="str">
+        <v>Makassar New Port</v>
+      </c>
+      <c r="E458" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F458" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G458" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H458" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459">
+        <v>2026</v>
+      </c>
+      <c r="B459">
+        <v>10</v>
+      </c>
+      <c r="C459" t="str">
+        <v>R24</v>
+      </c>
+      <c r="D459" t="str">
+        <v>Makassar New Port</v>
+      </c>
+      <c r="E459" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F459" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G459" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H459">
+        <v>45.4</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460">
+        <v>2026</v>
+      </c>
+      <c r="B460">
+        <v>10</v>
+      </c>
+      <c r="C460" t="str">
+        <v>R24</v>
+      </c>
+      <c r="D460" t="str">
+        <v>Makassar New Port</v>
+      </c>
+      <c r="E460" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F460" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G460" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H460">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461">
+        <v>2026</v>
+      </c>
+      <c r="B461">
+        <v>10</v>
+      </c>
+      <c r="C461" t="str">
+        <v>R25</v>
+      </c>
+      <c r="D461" t="str">
+        <v>Bontang</v>
+      </c>
+      <c r="E461" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F461" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G461" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H461">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462">
+        <v>2026</v>
+      </c>
+      <c r="B462">
+        <v>10</v>
+      </c>
+      <c r="C462" t="str">
+        <v>R25</v>
+      </c>
+      <c r="D462" t="str">
+        <v>Bontang</v>
+      </c>
+      <c r="E462" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F462" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G462" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H462">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463">
+        <v>2026</v>
+      </c>
+      <c r="B463">
+        <v>10</v>
+      </c>
+      <c r="C463" t="str">
+        <v>R25</v>
+      </c>
+      <c r="D463" t="str">
+        <v>Bontang</v>
+      </c>
+      <c r="E463" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F463" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G463" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H463">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464">
+        <v>2026</v>
+      </c>
+      <c r="B464">
+        <v>10</v>
+      </c>
+      <c r="C464" t="str">
+        <v>R25</v>
+      </c>
+      <c r="D464" t="str">
+        <v>Bontang</v>
+      </c>
+      <c r="E464" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F464" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G464" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H464">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465">
+        <v>2026</v>
+      </c>
+      <c r="B465">
+        <v>10</v>
+      </c>
+      <c r="C465" t="str">
+        <v>R25</v>
+      </c>
+      <c r="D465" t="str">
+        <v>Bontang</v>
+      </c>
+      <c r="E465" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F465" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G465" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H465">
+        <v>3927</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466">
+        <v>2026</v>
+      </c>
+      <c r="B466">
+        <v>10</v>
+      </c>
+      <c r="C466" t="str">
+        <v>R25</v>
+      </c>
+      <c r="D466" t="str">
+        <v>Bontang</v>
+      </c>
+      <c r="E466" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F466" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G466" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H466">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467">
+        <v>2026</v>
+      </c>
+      <c r="B467">
+        <v>10</v>
+      </c>
+      <c r="C467" t="str">
+        <v>R25</v>
+      </c>
+      <c r="D467" t="str">
+        <v>Bontang</v>
+      </c>
+      <c r="E467" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F467" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G467" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H467">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468">
+        <v>2026</v>
+      </c>
+      <c r="B468">
+        <v>10</v>
+      </c>
+      <c r="C468" t="str">
+        <v>R25</v>
+      </c>
+      <c r="D468" t="str">
+        <v>Bontang</v>
+      </c>
+      <c r="E468" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F468" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G468" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H468">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469">
+        <v>2026</v>
+      </c>
+      <c r="B469">
+        <v>10</v>
+      </c>
+      <c r="C469" t="str">
+        <v>R25</v>
+      </c>
+      <c r="D469" t="str">
+        <v>Bontang</v>
+      </c>
+      <c r="E469" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F469" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G469" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H469">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470">
+        <v>2026</v>
+      </c>
+      <c r="B470">
+        <v>10</v>
+      </c>
+      <c r="C470" t="str">
+        <v>R26</v>
+      </c>
+      <c r="D470" t="str">
+        <v>KKT</v>
+      </c>
+      <c r="E470" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F470" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G470" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H470">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471">
+        <v>2026</v>
+      </c>
+      <c r="B471">
+        <v>10</v>
+      </c>
+      <c r="C471" t="str">
+        <v>R26</v>
+      </c>
+      <c r="D471" t="str">
+        <v>KKT</v>
+      </c>
+      <c r="E471" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F471" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G471" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H471">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472">
+        <v>2026</v>
+      </c>
+      <c r="B472">
+        <v>10</v>
+      </c>
+      <c r="C472" t="str">
+        <v>R26</v>
+      </c>
+      <c r="D472" t="str">
+        <v>KKT</v>
+      </c>
+      <c r="E472" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F472" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G472" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H472">
+        <v>3672</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473">
+        <v>2026</v>
+      </c>
+      <c r="B473">
+        <v>10</v>
+      </c>
+      <c r="C473" t="str">
+        <v>R26</v>
+      </c>
+      <c r="D473" t="str">
+        <v>KKT</v>
+      </c>
+      <c r="E473" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F473" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G473" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H473">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474">
+        <v>2026</v>
+      </c>
+      <c r="B474">
+        <v>10</v>
+      </c>
+      <c r="C474" t="str">
+        <v>R26</v>
+      </c>
+      <c r="D474" t="str">
+        <v>KKT</v>
+      </c>
+      <c r="E474" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F474" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G474" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H474">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475">
+        <v>2026</v>
+      </c>
+      <c r="B475">
+        <v>10</v>
+      </c>
+      <c r="C475" t="str">
+        <v>R26</v>
+      </c>
+      <c r="D475" t="str">
+        <v>KKT</v>
+      </c>
+      <c r="E475" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F475" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G475" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H475">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476">
+        <v>2026</v>
+      </c>
+      <c r="B476">
+        <v>10</v>
+      </c>
+      <c r="C476" t="str">
+        <v>R26</v>
+      </c>
+      <c r="D476" t="str">
+        <v>KKT</v>
+      </c>
+      <c r="E476" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F476" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G476" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H476">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477">
+        <v>2026</v>
+      </c>
+      <c r="B477">
+        <v>10</v>
+      </c>
+      <c r="C477" t="str">
+        <v>R26</v>
+      </c>
+      <c r="D477" t="str">
+        <v>KKT</v>
+      </c>
+      <c r="E477" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F477" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G477" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H477">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478">
+        <v>2026</v>
+      </c>
+      <c r="B478">
+        <v>10</v>
+      </c>
+      <c r="C478" t="str">
+        <v>R26</v>
+      </c>
+      <c r="D478" t="str">
+        <v>KKT</v>
+      </c>
+      <c r="E478" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F478" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G478" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H478">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479">
+        <v>2026</v>
+      </c>
+      <c r="B479">
+        <v>10</v>
+      </c>
+      <c r="C479" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D479" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E479" t="str">
+        <v>K01</v>
+      </c>
+      <c r="F479" t="str">
+        <v>KAPAL</v>
+      </c>
+      <c r="G479" t="str">
+        <v>WTP</v>
+      </c>
+      <c r="H479">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480">
+        <v>2026</v>
+      </c>
+      <c r="B480">
+        <v>10</v>
+      </c>
+      <c r="C480" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D480" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E480" t="str">
+        <v>K02</v>
+      </c>
+      <c r="F480" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G480" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H480">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481">
+        <v>2026</v>
+      </c>
+      <c r="B481">
+        <v>10</v>
+      </c>
+      <c r="C481" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D481" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E481" t="str">
+        <v>K03</v>
+      </c>
+      <c r="F481" t="str">
+        <v>CURAH KERING</v>
+      </c>
+      <c r="G481" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H481">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482">
+        <v>2026</v>
+      </c>
+      <c r="B482">
+        <v>10</v>
+      </c>
+      <c r="C482" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D482" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E482" t="str">
+        <v>K04</v>
+      </c>
+      <c r="F482" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G482" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H482">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483">
+        <v>2026</v>
+      </c>
+      <c r="B483">
+        <v>10</v>
+      </c>
+      <c r="C483" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D483" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E483" t="str">
+        <v>K05</v>
+      </c>
+      <c r="F483" t="str">
+        <v>CURAH CAIR</v>
+      </c>
+      <c r="G483" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H483">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484">
+        <v>2026</v>
+      </c>
+      <c r="B484">
+        <v>10</v>
+      </c>
+      <c r="C484" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D484" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E484" t="str">
+        <v>K06</v>
+      </c>
+      <c r="F484" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G484" t="str">
+        <v>TGH</v>
+      </c>
+      <c r="H484">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485">
+        <v>2026</v>
+      </c>
+      <c r="B485">
+        <v>10</v>
+      </c>
+      <c r="C485" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D485" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E485" t="str">
+        <v>K07</v>
+      </c>
+      <c r="F485" t="str">
+        <v>GENERAL CARGO</v>
+      </c>
+      <c r="G485" t="str">
+        <v>TSD</v>
+      </c>
+      <c r="H485">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486">
+        <v>2026</v>
+      </c>
+      <c r="B486">
+        <v>10</v>
+      </c>
+      <c r="C486" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D486" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E486" t="str">
+        <v>K08</v>
+      </c>
+      <c r="F486" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G486" t="str">
+        <v>BSH</v>
+      </c>
+      <c r="H486">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487">
+        <v>2026</v>
+      </c>
+      <c r="B487">
+        <v>10</v>
+      </c>
+      <c r="C487" t="str">
+        <v>R80</v>
+      </c>
+      <c r="D487" t="str">
+        <v>Luwuk Tangkiang</v>
+      </c>
+      <c r="E487" t="str">
+        <v>K09</v>
+      </c>
+      <c r="F487" t="str">
+        <v>PETIKEMAS</v>
+      </c>
+      <c r="G487" t="str">
+        <v>BCH</v>
+      </c>
+      <c r="H487">
+        <v>12.8</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H487"/>
   </ignoredErrors>
 </worksheet>
 </file>
